--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -37,11 +37,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,17 +65,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -150,6 +157,596 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Abonnés</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>abonnés</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues par jour : vidéos et stories</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D5AFE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$E$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$L$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Portée du compte et visites du profil</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="8E5CFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="8E5CFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$F$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="00B8D4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B8D4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$H$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Abonnés gagnés par jour</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$C$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>14</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -526,8 +1123,54 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <f>IF(ROW()=2,"",B2-B1)</f>
+        <v/>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <f>IF(ROW()=2,D2,D2-D1)</f>
+        <v/>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -627,7 +1270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -637,6 +1280,13 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Jour</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -651,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -668,6 +1318,17 @@
         <is>
           <t>Total du jour</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>SUM(B2:A2)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -760,56 +1421,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Décodé · suivi du compte Décodé - la science simplement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Mis à jour automatiquement par l'agent 3 à chaque relevé (9 h et 16 h, heure de Paris).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Source : API Instagram (insights). Les vues et partages sont cumulés depuis la publication.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>« Abonnés gagnés » et « Vues du jour » = différence avec le relevé de la veille (formules).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>« Vues du jour par vidéo » = vues gagnées par chaque vidéo depuis le relevé de la veille.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>« Heure par heure » : relevé toutes les heures de 7 h à 23 h (Paris) ; le relevé de 7 h inclut la nuit.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Les statistiques d'une story ne sont lisibles que pendant ses 24 h : dernier relevé conservé.</t>
         </is>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -210,12 +210,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2</f>
+              <f>'Jour par jour'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -312,12 +312,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2</f>
+              <f>'Jour par jour'!$E$2:$E$3</f>
             </numRef>
           </val>
         </ser>
@@ -339,12 +339,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2</f>
+              <f>'Jour par jour'!$L$2:$L$3</f>
             </numRef>
           </val>
         </ser>
@@ -452,12 +452,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2</f>
+              <f>'Jour par jour'!$F$2:$F$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -492,12 +492,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2</f>
+              <f>'Jour par jour'!$H$2:$H$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -594,12 +594,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2</f>
+              <f>'Jour par jour'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2</f>
+              <f>'Jour par jour'!$C$2:$C$3</f>
             </numRef>
           </val>
         </ser>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1165,6 +1165,51 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <f>IF(ROW()=2,"",B3-B2)</f>
+        <v/>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <f>IF(ROW()=2,D3,D3-D2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1270,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1287,6 +1332,13 @@
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1328,6 +1380,17 @@
       </c>
       <c r="B2" s="3">
         <f>SUM(B2:A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>SUM(B3:A3)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -11,8 +11,10 @@
     <sheet name="Vidéos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Évolution par vidéo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Vues du jour par vidéo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Stories" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="À lire" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Heure par heure" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Vues gagnées par heure" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Stories" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="À lire" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,6 +658,422 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues cumulées de chaque vidéo, heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$C$2:$C$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Abonnés, heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="E5133A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$B$2:$B$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues totales du compte (vidéos), heure par heure</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="3D5AFE"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="3D5AFE"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$D$2:$D$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues gagnées chaque heure, vidéo par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$B$2:$B$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -741,6 +1159,104 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1405,6 +1921,897 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Abonnés</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>10-27 Comment ce robot canar</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Vues totales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 10:00</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3">
+        <f>SUM(C2:C2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 11:00</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3">
+        <f>SUM(C3:C3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:00</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3">
+        <f>SUM(C4:C4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:00</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3">
+        <f>SUM(C5:C5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:00</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3">
+        <f>SUM(C6:C6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 15:00</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3">
+        <f>SUM(C7:C7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 16:00</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3">
+        <f>SUM(C8:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 17:00</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3">
+        <f>SUM(C9:C9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 18:00</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3">
+        <f>SUM(C10:C10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 19:00</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3">
+        <f>SUM(C11:C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 20:00</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3">
+        <f>SUM(C12:C12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:00</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3">
+        <f>SUM(C13:C13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25 22:00</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3">
+        <f>SUM(C14:C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:00</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3">
+        <f>SUM(C15:C15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:00</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3">
+        <f>SUM(C16:C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:00</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3">
+        <f>SUM(C17:C17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:00</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3">
+        <f>SUM(C18:C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:00</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3">
+        <f>SUM(C19:C19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:00</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3">
+        <f>SUM(C20:C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:00</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3">
+        <f>SUM(C21:C21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:00</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3">
+        <f>SUM(C22:C22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:00</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3">
+        <f>SUM(C23:C23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 17:00</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3">
+        <f>SUM(C24:C24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 18:00</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3">
+        <f>SUM(C25:C25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 19:00</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3">
+        <f>SUM(C26:C26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 20:00</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3">
+        <f>SUM(C27:C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26 21:00</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3">
+        <f>SUM(C28:C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 08:00</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Heure</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>10-27 Comment ce robot canar</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total de l'heure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <f>'Heure par heure'!A2</f>
+        <v/>
+      </c>
+      <c r="B2" s="3" t="inlineStr"/>
+      <c r="C2" s="3">
+        <f>SUM(B2:B2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <f>'Heure par heure'!A3</f>
+        <v/>
+      </c>
+      <c r="B3" s="3">
+        <f>IF('Heure par heure'!C3="","",'Heure par heure'!C3-N('Heure par heure'!C2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>SUM(B3:B3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <f>'Heure par heure'!A4</f>
+        <v/>
+      </c>
+      <c r="B4" s="3">
+        <f>IF('Heure par heure'!C4="","",'Heure par heure'!C4-N('Heure par heure'!C3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>SUM(B4:B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <f>'Heure par heure'!A5</f>
+        <v/>
+      </c>
+      <c r="B5" s="3">
+        <f>IF('Heure par heure'!C5="","",'Heure par heure'!C5-N('Heure par heure'!C4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>SUM(B5:B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <f>'Heure par heure'!A6</f>
+        <v/>
+      </c>
+      <c r="B6" s="3">
+        <f>IF('Heure par heure'!C6="","",'Heure par heure'!C6-N('Heure par heure'!C5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>SUM(B6:B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <f>'Heure par heure'!A7</f>
+        <v/>
+      </c>
+      <c r="B7" s="3">
+        <f>IF('Heure par heure'!C7="","",'Heure par heure'!C7-N('Heure par heure'!C6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>SUM(B7:B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <f>'Heure par heure'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="3">
+        <f>IF('Heure par heure'!C8="","",'Heure par heure'!C8-N('Heure par heure'!C7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>SUM(B8:B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <f>'Heure par heure'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="3">
+        <f>IF('Heure par heure'!C9="","",'Heure par heure'!C9-N('Heure par heure'!C8))</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>SUM(B9:B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <f>'Heure par heure'!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="3">
+        <f>IF('Heure par heure'!C10="","",'Heure par heure'!C10-N('Heure par heure'!C9))</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>SUM(B10:B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <f>'Heure par heure'!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="3">
+        <f>IF('Heure par heure'!C11="","",'Heure par heure'!C11-N('Heure par heure'!C10))</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>SUM(B11:B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <f>'Heure par heure'!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="3">
+        <f>IF('Heure par heure'!C12="","",'Heure par heure'!C12-N('Heure par heure'!C11))</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>SUM(B12:B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <f>'Heure par heure'!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="3">
+        <f>IF('Heure par heure'!C13="","",'Heure par heure'!C13-N('Heure par heure'!C12))</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>SUM(B13:B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <f>'Heure par heure'!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="3">
+        <f>IF('Heure par heure'!C14="","",'Heure par heure'!C14-N('Heure par heure'!C13))</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>SUM(B14:B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <f>'Heure par heure'!A15</f>
+        <v/>
+      </c>
+      <c r="B15" s="3">
+        <f>IF('Heure par heure'!C15="","",'Heure par heure'!C15-N('Heure par heure'!C14))</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>SUM(B15:B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <f>'Heure par heure'!A16</f>
+        <v/>
+      </c>
+      <c r="B16" s="3">
+        <f>IF('Heure par heure'!C16="","",'Heure par heure'!C16-N('Heure par heure'!C15))</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>SUM(B16:B16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <f>'Heure par heure'!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="3">
+        <f>IF('Heure par heure'!C17="","",'Heure par heure'!C17-N('Heure par heure'!C16))</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>SUM(B17:B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <f>'Heure par heure'!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="3">
+        <f>IF('Heure par heure'!C18="","",'Heure par heure'!C18-N('Heure par heure'!C17))</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>SUM(B18:B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <f>'Heure par heure'!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="3">
+        <f>IF('Heure par heure'!C19="","",'Heure par heure'!C19-N('Heure par heure'!C18))</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>SUM(B19:B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <f>'Heure par heure'!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="3">
+        <f>IF('Heure par heure'!C20="","",'Heure par heure'!C20-N('Heure par heure'!C19))</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>SUM(B20:B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <f>'Heure par heure'!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="3">
+        <f>IF('Heure par heure'!C21="","",'Heure par heure'!C21-N('Heure par heure'!C20))</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>SUM(B21:B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <f>'Heure par heure'!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="3">
+        <f>IF('Heure par heure'!C22="","",'Heure par heure'!C22-N('Heure par heure'!C21))</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>SUM(B22:B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <f>'Heure par heure'!A23</f>
+        <v/>
+      </c>
+      <c r="B23" s="3">
+        <f>IF('Heure par heure'!C23="","",'Heure par heure'!C23-N('Heure par heure'!C22))</f>
+        <v/>
+      </c>
+      <c r="C23" s="3">
+        <f>SUM(B23:B23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <f>'Heure par heure'!A24</f>
+        <v/>
+      </c>
+      <c r="B24" s="3">
+        <f>IF('Heure par heure'!C24="","",'Heure par heure'!C24-N('Heure par heure'!C23))</f>
+        <v/>
+      </c>
+      <c r="C24" s="3">
+        <f>SUM(B24:B24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <f>'Heure par heure'!A25</f>
+        <v/>
+      </c>
+      <c r="B25" s="3">
+        <f>IF('Heure par heure'!C25="","",'Heure par heure'!C25-N('Heure par heure'!C24))</f>
+        <v/>
+      </c>
+      <c r="C25" s="3">
+        <f>SUM(B25:B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <f>'Heure par heure'!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="3">
+        <f>IF('Heure par heure'!C26="","",'Heure par heure'!C26-N('Heure par heure'!C25))</f>
+        <v/>
+      </c>
+      <c r="C26" s="3">
+        <f>SUM(B26:B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <f>'Heure par heure'!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="3">
+        <f>IF('Heure par heure'!C27="","",'Heure par heure'!C27-N('Heure par heure'!C26))</f>
+        <v/>
+      </c>
+      <c r="C27" s="3">
+        <f>SUM(B27:B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <f>'Heure par heure'!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="3">
+        <f>IF('Heure par heure'!C28="","",'Heure par heure'!C28-N('Heure par heure'!C27))</f>
+        <v/>
+      </c>
+      <c r="C28" s="3">
+        <f>SUM(B28:B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <f>'Heure par heure'!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="3">
+        <f>IF('Heure par heure'!C29="","",'Heure par heure'!C29-N('Heure par heure'!C28))</f>
+        <v/>
+      </c>
+      <c r="C29" s="3">
+        <f>SUM(B29:B29)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1471,7 +2878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -23,8 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +41,11 @@
     </font>
     <font>
       <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -76,14 +83,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -212,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
+              <f>'Jour par jour'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$3</f>
+              <f>'Jour par jour'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -274,391 +284,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Vues par jour : vidéos et stories</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Jour par jour'!E1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="3D5AFE"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Jour par jour'!$E$2:$E$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Jour par jour'!L1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF8A1F"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Jour par jour'!$L$2:$L$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Portée du compte et visites du profil</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Jour par jour'!F1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="28000">
-              <a:solidFill>
-                <a:srgbClr val="8E5CFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="8E5CFF"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Jour par jour'!$F$2:$F$3</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Jour par jour'!H1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="28000">
-              <a:solidFill>
-                <a:srgbClr val="00B8D4"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B8D4"/>
-              </a:solidFill>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Jour par jour'!$H$2:$H$3</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Abonnés gagnés par jour</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Jour par jour'!C1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="2E7D32"/>
-            </a:solidFill>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Jour par jour'!$A$2:$A$3</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Jour par jour'!$C$2:$C$3</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -763,7 +389,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -876,7 +502,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -989,7 +615,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1032,6 +658,1069 @@
           <val>
             <numRef>
               <f>'Vues gagnées par heure'!$B$2:$B$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues des stories</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Stories'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Stories'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Stories'!$B$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues par jour : vidéos et stories</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D5AFE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$E$2:$E$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!L1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$L$2:$L$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Portée du compte et visites du profil</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="8E5CFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="8E5CFF"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$F$2:$F$4</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="00B8D4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B8D4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$H$2:$H$4</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Abonnés gagnés par jour</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Jour par jour'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jour par jour'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jour par jour'!$C$2:$C$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3D5AFE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$D$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Likes, commentaires, partages, enregistrements</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF4F81"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$F$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8E5CFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$G$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E7D32"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$H$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF8A1F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$I$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Taux d'engagement</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vidéos'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E5133A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vidéos'!$B$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vidéos'!$K$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues cumulées de chaque vidéo, jour après jour</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$B$2:$B$4</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Vues gagnées chaque jour, vidéo par vidéo</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -1173,6 +1862,131 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>31</row>
       <rowOff>0</rowOff>
     </from>
@@ -1238,7 +2052,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1248,6 +2062,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2700000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1554,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1729,6 +2570,51 @@
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <f>IF(ROW()=2,"",B4-B3)</f>
+        <v/>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3">
+        <f>IF(ROW()=2,D4,D4-D3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1741,7 +2627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1820,8 +2706,58 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:14</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comment ce robot canard tient sur 2 pattes à </t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
+        <v/>
+      </c>
+      <c r="L2" s="6">
+        <f>IFERROR(D2/E2,0)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1831,10 +2767,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1843,6 +2780,11 @@
           <t>Jour</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Comment ce robot canard tien</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1850,6 +2792,7 @@
           <t>2026-10-25</t>
         </is>
       </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1857,9 +2800,21 @@
           <t>2026-10-26</t>
         </is>
       </c>
+      <c r="B3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1869,11 +2824,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1884,6 +2840,11 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Comment ce robot canard tien</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -1895,7 +2856,11 @@
         </is>
       </c>
       <c r="B2" s="3">
-        <f>SUM(B2:A2)</f>
+        <f>IF('Évolution par vidéo'!B2="","",'Évolution par vidéo'!B2)</f>
+        <v/>
+      </c>
+      <c r="C2" s="3">
+        <f>SUM(B2:B2)</f>
         <v/>
       </c>
     </row>
@@ -1906,12 +2871,32 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>SUM(B3:A3)</f>
+        <f>IF('Évolution par vidéo'!B3="","",'Évolution par vidéo'!B3-N('Évolution par vidéo'!B2))</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>SUM(B3:B3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>IF('Évolution par vidéo'!B4="","",'Évolution par vidéo'!B4-N('Évolution par vidéo'!B3))</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>SUM(B4:B4)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2812,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2873,8 +3858,45 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:14</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2891,56 +3913,56 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Décodé · suivi du compte Décodé - la science simplement</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Mis à jour automatiquement par l'agent 3 à chaque relevé (9 h et 16 h, heure de Paris).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Source : API Instagram (insights). Les vues et partages sont cumulés depuis la publication.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>« Abonnés gagnés » et « Vues du jour » = différence avec le relevé de la veille (formules).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>« Vues du jour par vidéo » = vues gagnées par chaque vidéo depuis le relevé de la veille.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>« Heure par heure » : relevé toutes les heures de 7 h à 23 h (Paris) ; le relevé de 7 h inclut la nuit.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Taux d'engagement = (likes + commentaires + partages + enregistrements) / comptes touchés.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Les statistiques d'une story ne sont lisibles que pendant ses 24 h : dernier relevé conservé.</t>
         </is>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$29</f>
+              <f>'Heure par heure'!$C$2:$C$30</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$29</f>
+              <f>'Heure par heure'!$B$2:$B$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$29</f>
+              <f>'Heure par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$29</f>
+              <f>'Heure par heure'!$D$2:$D$30</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$29</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$29</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$30</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>32</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3356,23 @@
       </c>
       <c r="D29" s="3">
         <f>SUM(C29:C29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D30" s="3">
+        <f>SUM(C30:C30)</f>
         <v/>
       </c>
     </row>
@@ -3371,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3782,6 +3799,20 @@
       </c>
       <c r="C29" s="3">
         <f>SUM(B29:B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <f>'Heure par heure'!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="3">
+        <f>IF('Heure par heure'!C30="","",'Heure par heure'!C30-N('Heure par heure'!C29))</f>
+        <v/>
+      </c>
+      <c r="C30" s="3">
+        <f>SUM(B30:B30)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$30</f>
+              <f>'Heure par heure'!$C$2:$C$31</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$30</f>
+              <f>'Heure par heure'!$B$2:$B$31</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$30</f>
+              <f>'Heure par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$30</f>
+              <f>'Heure par heure'!$D$2:$D$31</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$30</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$30</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$31</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3373,6 +3373,23 @@
       </c>
       <c r="D30" s="3">
         <f>SUM(C30:C30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:00</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D31" s="3">
+        <f>SUM(C31:C31)</f>
         <v/>
       </c>
     </row>
@@ -3388,7 +3405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3813,6 +3830,20 @@
       </c>
       <c r="C30" s="3">
         <f>SUM(B30:B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <f>'Heure par heure'!A31</f>
+        <v/>
+      </c>
+      <c r="B31" s="3">
+        <f>IF('Heure par heure'!C31="","",'Heure par heure'!C31-N('Heure par heure'!C30))</f>
+        <v/>
+      </c>
+      <c r="C31" s="3">
+        <f>SUM(B31:B31)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$31</f>
+              <f>'Heure par heure'!$C$2:$C$32</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$31</f>
+              <f>'Heure par heure'!$B$2:$B$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$31</f>
+              <f>'Heure par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$31</f>
+              <f>'Heure par heure'!$D$2:$D$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$31</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$31</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3390,6 +3390,23 @@
       </c>
       <c r="D31" s="3">
         <f>SUM(C31:C31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:00</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D32" s="3">
+        <f>SUM(C32:C32)</f>
         <v/>
       </c>
     </row>
@@ -3405,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3844,6 +3861,20 @@
       </c>
       <c r="C31" s="3">
         <f>SUM(B31:B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <f>'Heure par heure'!A32</f>
+        <v/>
+      </c>
+      <c r="B32" s="3">
+        <f>IF('Heure par heure'!C32="","",'Heure par heure'!C32-N('Heure par heure'!C31))</f>
+        <v/>
+      </c>
+      <c r="C32" s="3">
+        <f>SUM(B32:B32)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$32</f>
+              <f>'Heure par heure'!$C$2:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$32</f>
+              <f>'Heure par heure'!$B$2:$B$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$32</f>
+              <f>'Heure par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$32</f>
+              <f>'Heure par heure'!$D$2:$D$33</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$32</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$32</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$33</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3407,6 +3407,23 @@
       </c>
       <c r="D32" s="3">
         <f>SUM(C32:C32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:00</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D33" s="3">
+        <f>SUM(C33:C33)</f>
         <v/>
       </c>
     </row>
@@ -3422,7 +3439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3875,6 +3892,20 @@
       </c>
       <c r="C32" s="3">
         <f>SUM(B32:B32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <f>'Heure par heure'!A33</f>
+        <v/>
+      </c>
+      <c r="B33" s="3">
+        <f>IF('Heure par heure'!C33="","",'Heure par heure'!C33-N('Heure par heure'!C32))</f>
+        <v/>
+      </c>
+      <c r="C33" s="3">
+        <f>SUM(B33:B33)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$33</f>
+              <f>'Heure par heure'!$C$2:$C$34</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$33</f>
+              <f>'Heure par heure'!$B$2:$B$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$33</f>
+              <f>'Heure par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$33</f>
+              <f>'Heure par heure'!$D$2:$D$34</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$33</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$33</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$34</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3424,6 +3424,23 @@
       </c>
       <c r="D33" s="3">
         <f>SUM(C33:C33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:00</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D34" s="3">
+        <f>SUM(C34:C34)</f>
         <v/>
       </c>
     </row>
@@ -3439,7 +3456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3906,6 +3923,20 @@
       </c>
       <c r="C33" s="3">
         <f>SUM(B33:B33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <f>'Heure par heure'!A34</f>
+        <v/>
+      </c>
+      <c r="B34" s="3">
+        <f>IF('Heure par heure'!C34="","",'Heure par heure'!C34-N('Heure par heure'!C33))</f>
+        <v/>
+      </c>
+      <c r="C34" s="3">
+        <f>SUM(B34:B34)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$34</f>
+              <f>'Heure par heure'!$C$2:$C$35</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$34</f>
+              <f>'Heure par heure'!$B$2:$B$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$34</f>
+              <f>'Heure par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$34</f>
+              <f>'Heure par heure'!$D$2:$D$35</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$34</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$34</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$35</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3441,6 +3441,23 @@
       </c>
       <c r="D34" s="3">
         <f>SUM(C34:C34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D35" s="3">
+        <f>SUM(C35:C35)</f>
         <v/>
       </c>
     </row>
@@ -3456,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3937,6 +3954,20 @@
       </c>
       <c r="C34" s="3">
         <f>SUM(B34:B34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <f>'Heure par heure'!A35</f>
+        <v/>
+      </c>
+      <c r="B35" s="3">
+        <f>IF('Heure par heure'!C35="","",'Heure par heure'!C35-N('Heure par heure'!C34))</f>
+        <v/>
+      </c>
+      <c r="C35" s="3">
+        <f>SUM(B35:B35)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$35</f>
+              <f>'Heure par heure'!$C$2:$C$36</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$35</f>
+              <f>'Heure par heure'!$B$2:$B$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$35</f>
+              <f>'Heure par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$35</f>
+              <f>'Heure par heure'!$D$2:$D$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$35</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$35</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$36</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3458,6 +3458,23 @@
       </c>
       <c r="D35" s="3">
         <f>SUM(C35:C35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D36" s="3">
+        <f>SUM(C36:C36)</f>
         <v/>
       </c>
     </row>
@@ -3473,7 +3490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3968,6 +3985,20 @@
       </c>
       <c r="C35" s="3">
         <f>SUM(B35:B35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <f>'Heure par heure'!A36</f>
+        <v/>
+      </c>
+      <c r="B36" s="3">
+        <f>IF('Heure par heure'!C36="","",'Heure par heure'!C36-N('Heure par heure'!C35))</f>
+        <v/>
+      </c>
+      <c r="C36" s="3">
+        <f>SUM(B36:B36)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -2584,26 +2584,26 @@
         <v/>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="E4" s="3">
         <f>IF(ROW()=2,D4,D4-D3)</f>
         <v/>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>7</v>
+        <v>119</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="5">
         <f>IFERROR((F2+G2+H2+I2)/IF(E2&gt;0,E2,D2),0)</f>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$36</f>
+              <f>'Heure par heure'!$C$2:$C$37</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$36</f>
+              <f>'Heure par heure'!$B$2:$B$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$36</f>
+              <f>'Heure par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$36</f>
+              <f>'Heure par heure'!$D$2:$D$37</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$36</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$36</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$37</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3475,6 +3475,23 @@
       </c>
       <c r="D36" s="3">
         <f>SUM(C36:C36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:00</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D37" s="3">
+        <f>SUM(C37:C37)</f>
         <v/>
       </c>
     </row>
@@ -3490,7 +3507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3999,6 +4016,20 @@
       </c>
       <c r="C36" s="3">
         <f>SUM(B36:B36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <f>'Heure par heure'!A37</f>
+        <v/>
+      </c>
+      <c r="B37" s="3">
+        <f>IF('Heure par heure'!C37="","",'Heure par heure'!C37-N('Heure par heure'!C36))</f>
+        <v/>
+      </c>
+      <c r="C37" s="3">
+        <f>SUM(B37:B37)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$37</f>
+              <f>'Heure par heure'!$C$2:$C$38</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$37</f>
+              <f>'Heure par heure'!$B$2:$B$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$37</f>
+              <f>'Heure par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$37</f>
+              <f>'Heure par heure'!$D$2:$D$38</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$37</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$37</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$38</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3492,6 +3492,23 @@
       </c>
       <c r="D37" s="3">
         <f>SUM(C37:C37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:00</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D38" s="3">
+        <f>SUM(C38:C38)</f>
         <v/>
       </c>
     </row>
@@ -3507,7 +3524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4030,6 +4047,20 @@
       </c>
       <c r="C37" s="3">
         <f>SUM(B37:B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <f>'Heure par heure'!A38</f>
+        <v/>
+      </c>
+      <c r="B38" s="3">
+        <f>IF('Heure par heure'!C38="","",'Heure par heure'!C38-N('Heure par heure'!C37))</f>
+        <v/>
+      </c>
+      <c r="C38" s="3">
+        <f>SUM(B38:B38)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$38</f>
+              <f>'Heure par heure'!$C$2:$C$39</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$38</f>
+              <f>'Heure par heure'!$B$2:$B$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$38</f>
+              <f>'Heure par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$38</f>
+              <f>'Heure par heure'!$D$2:$D$39</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$38</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$38</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$39</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3509,6 +3509,23 @@
       </c>
       <c r="D38" s="3">
         <f>SUM(C38:C38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 18:00</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D39" s="3">
+        <f>SUM(C39:C39)</f>
         <v/>
       </c>
     </row>
@@ -3524,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4061,6 +4078,20 @@
       </c>
       <c r="C38" s="3">
         <f>SUM(B38:B38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <f>'Heure par heure'!A39</f>
+        <v/>
+      </c>
+      <c r="B39" s="3">
+        <f>IF('Heure par heure'!C39="","",'Heure par heure'!C39-N('Heure par heure'!C38))</f>
+        <v/>
+      </c>
+      <c r="C39" s="3">
+        <f>SUM(B39:B39)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$39</f>
+              <f>'Heure par heure'!$C$2:$C$40</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +440,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$39</f>
+              <f>'Heure par heure'!$B$2:$B$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -553,12 +553,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$39</f>
+              <f>'Heure par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$39</f>
+              <f>'Heure par heure'!$D$2:$D$40</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +652,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$39</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$39</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$40</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +1987,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2009,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2031,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2058,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3526,6 +3526,23 @@
       </c>
       <c r="D39" s="3">
         <f>SUM(C39:C39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:00</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D40" s="3">
+        <f>SUM(C40:C40)</f>
         <v/>
       </c>
     </row>
@@ -3541,7 +3558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4092,6 +4109,20 @@
       </c>
       <c r="C39" s="3">
         <f>SUM(B39:B39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <f>'Heure par heure'!A40</f>
+        <v/>
+      </c>
+      <c r="B40" s="3">
+        <f>IF('Heure par heure'!C40="","",'Heure par heure'!C40-N('Heure par heure'!C39))</f>
+        <v/>
+      </c>
+      <c r="C40" s="3">
+        <f>SUM(B40:B40)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$40</f>
+              <f>'Heure par heure'!$C$2:$C$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$D$2:$D$41</f>
             </numRef>
           </val>
         </ser>
@@ -440,12 +472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$40</f>
+              <f>'Heure par heure'!$B$2:$B$41</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -528,7 +560,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Heure par heure'!D1</f>
+              <f>'Heure par heure'!E1</f>
             </strRef>
           </tx>
           <spPr>
@@ -553,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$40</f>
+              <f>'Heure par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$40</f>
+              <f>'Heure par heure'!$E$2:$E$41</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -652,12 +684,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$40</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$40</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$C$2:$C$41</f>
             </numRef>
           </val>
         </ser>
@@ -1987,7 +2043,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2009,7 +2065,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2031,7 +2087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2058,7 +2114,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2906,13 +2962,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2933,6 +2990,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>10-27 Pourquoi un avion de 5</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Vues totales</t>
         </is>
       </c>
@@ -2947,8 +3009,9 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3">
-        <f>SUM(C2:C2)</f>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3">
+        <f>SUM(C2:D2)</f>
         <v/>
       </c>
     </row>
@@ -2962,8 +3025,9 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3">
-        <f>SUM(C3:C3)</f>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3">
+        <f>SUM(C3:D3)</f>
         <v/>
       </c>
     </row>
@@ -2977,8 +3041,9 @@
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3">
-        <f>SUM(C4:C4)</f>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3">
+        <f>SUM(C4:D4)</f>
         <v/>
       </c>
     </row>
@@ -2992,8 +3057,9 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3">
-        <f>SUM(C5:C5)</f>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3">
+        <f>SUM(C5:D5)</f>
         <v/>
       </c>
     </row>
@@ -3007,8 +3073,9 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3">
-        <f>SUM(C6:C6)</f>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3">
+        <f>SUM(C6:D6)</f>
         <v/>
       </c>
     </row>
@@ -3022,8 +3089,9 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3">
-        <f>SUM(C7:C7)</f>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3">
+        <f>SUM(C7:D7)</f>
         <v/>
       </c>
     </row>
@@ -3037,8 +3105,9 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3">
-        <f>SUM(C8:C8)</f>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3">
+        <f>SUM(C8:D8)</f>
         <v/>
       </c>
     </row>
@@ -3052,8 +3121,9 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3">
-        <f>SUM(C9:C9)</f>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3">
+        <f>SUM(C9:D9)</f>
         <v/>
       </c>
     </row>
@@ -3067,8 +3137,9 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3">
-        <f>SUM(C10:C10)</f>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3">
+        <f>SUM(C10:D10)</f>
         <v/>
       </c>
     </row>
@@ -3082,8 +3153,9 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3">
-        <f>SUM(C11:C11)</f>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3">
+        <f>SUM(C11:D11)</f>
         <v/>
       </c>
     </row>
@@ -3097,8 +3169,9 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3">
-        <f>SUM(C12:C12)</f>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3">
+        <f>SUM(C12:D12)</f>
         <v/>
       </c>
     </row>
@@ -3112,8 +3185,9 @@
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3">
-        <f>SUM(C13:C13)</f>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3">
+        <f>SUM(C13:D13)</f>
         <v/>
       </c>
     </row>
@@ -3127,8 +3201,9 @@
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3">
-        <f>SUM(C14:C14)</f>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3">
+        <f>SUM(C14:D14)</f>
         <v/>
       </c>
     </row>
@@ -3142,8 +3217,9 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3">
-        <f>SUM(C15:C15)</f>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3">
+        <f>SUM(C15:D15)</f>
         <v/>
       </c>
     </row>
@@ -3157,8 +3233,9 @@
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3">
-        <f>SUM(C16:C16)</f>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3">
+        <f>SUM(C16:D16)</f>
         <v/>
       </c>
     </row>
@@ -3172,8 +3249,9 @@
         <v>0</v>
       </c>
       <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3">
-        <f>SUM(C17:C17)</f>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3">
+        <f>SUM(C17:D17)</f>
         <v/>
       </c>
     </row>
@@ -3187,8 +3265,9 @@
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3">
-        <f>SUM(C18:C18)</f>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3">
+        <f>SUM(C18:D18)</f>
         <v/>
       </c>
     </row>
@@ -3202,8 +3281,9 @@
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3">
-        <f>SUM(C19:C19)</f>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3">
+        <f>SUM(C19:D19)</f>
         <v/>
       </c>
     </row>
@@ -3217,8 +3297,9 @@
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3">
-        <f>SUM(C20:C20)</f>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3">
+        <f>SUM(C20:D20)</f>
         <v/>
       </c>
     </row>
@@ -3232,8 +3313,9 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3">
-        <f>SUM(C21:C21)</f>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3">
+        <f>SUM(C21:D21)</f>
         <v/>
       </c>
     </row>
@@ -3247,8 +3329,9 @@
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3">
-        <f>SUM(C22:C22)</f>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3">
+        <f>SUM(C22:D22)</f>
         <v/>
       </c>
     </row>
@@ -3262,8 +3345,9 @@
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3">
-        <f>SUM(C23:C23)</f>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3">
+        <f>SUM(C23:D23)</f>
         <v/>
       </c>
     </row>
@@ -3277,8 +3361,9 @@
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3">
-        <f>SUM(C24:C24)</f>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3">
+        <f>SUM(C24:D24)</f>
         <v/>
       </c>
     </row>
@@ -3292,8 +3377,9 @@
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3">
-        <f>SUM(C25:C25)</f>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3">
+        <f>SUM(C25:D25)</f>
         <v/>
       </c>
     </row>
@@ -3307,8 +3393,9 @@
         <v>0</v>
       </c>
       <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3">
-        <f>SUM(C26:C26)</f>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3">
+        <f>SUM(C26:D26)</f>
         <v/>
       </c>
     </row>
@@ -3322,8 +3409,9 @@
         <v>0</v>
       </c>
       <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3">
-        <f>SUM(C27:C27)</f>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3">
+        <f>SUM(C27:D27)</f>
         <v/>
       </c>
     </row>
@@ -3337,8 +3425,9 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3">
-        <f>SUM(C28:C28)</f>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3">
+        <f>SUM(C28:D28)</f>
         <v/>
       </c>
     </row>
@@ -3354,8 +3443,9 @@
       <c r="C29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="3">
-        <f>SUM(C29:C29)</f>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3">
+        <f>SUM(C29:D29)</f>
         <v/>
       </c>
     </row>
@@ -3371,8 +3461,9 @@
       <c r="C30" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D30" s="3">
-        <f>SUM(C30:C30)</f>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3">
+        <f>SUM(C30:D30)</f>
         <v/>
       </c>
     </row>
@@ -3388,8 +3479,9 @@
       <c r="C31" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="D31" s="3">
-        <f>SUM(C31:C31)</f>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3">
+        <f>SUM(C31:D31)</f>
         <v/>
       </c>
     </row>
@@ -3405,8 +3497,9 @@
       <c r="C32" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="D32" s="3">
-        <f>SUM(C32:C32)</f>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3">
+        <f>SUM(C32:D32)</f>
         <v/>
       </c>
     </row>
@@ -3422,8 +3515,9 @@
       <c r="C33" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="D33" s="3">
-        <f>SUM(C33:C33)</f>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3">
+        <f>SUM(C33:D33)</f>
         <v/>
       </c>
     </row>
@@ -3439,8 +3533,9 @@
       <c r="C34" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="D34" s="3">
-        <f>SUM(C34:C34)</f>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3">
+        <f>SUM(C34:D34)</f>
         <v/>
       </c>
     </row>
@@ -3456,8 +3551,9 @@
       <c r="C35" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="D35" s="3">
-        <f>SUM(C35:C35)</f>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3">
+        <f>SUM(C35:D35)</f>
         <v/>
       </c>
     </row>
@@ -3473,8 +3569,9 @@
       <c r="C36" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="D36" s="3">
-        <f>SUM(C36:C36)</f>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3">
+        <f>SUM(C36:D36)</f>
         <v/>
       </c>
     </row>
@@ -3490,8 +3587,9 @@
       <c r="C37" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="D37" s="3">
-        <f>SUM(C37:C37)</f>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3">
+        <f>SUM(C37:D37)</f>
         <v/>
       </c>
     </row>
@@ -3507,8 +3605,9 @@
       <c r="C38" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D38" s="3">
-        <f>SUM(C38:C38)</f>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3">
+        <f>SUM(C38:D38)</f>
         <v/>
       </c>
     </row>
@@ -3524,8 +3623,9 @@
       <c r="C39" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D39" s="3">
-        <f>SUM(C39:C39)</f>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3">
+        <f>SUM(C39:D39)</f>
         <v/>
       </c>
     </row>
@@ -3541,8 +3641,29 @@
       <c r="C40" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D40" s="3">
-        <f>SUM(C40:C40)</f>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3">
+        <f>SUM(C40:D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 20:00</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(C41:D41)</f>
         <v/>
       </c>
     </row>
@@ -3558,12 +3679,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3579,6 +3701,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>10-27 Pourquoi un avion de 5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Total de l'heure</t>
         </is>
       </c>
@@ -3589,8 +3716,9 @@
         <v/>
       </c>
       <c r="B2" s="3" t="inlineStr"/>
-      <c r="C2" s="3">
-        <f>SUM(B2:B2)</f>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3">
+        <f>SUM(B2:C2)</f>
         <v/>
       </c>
     </row>
@@ -3604,7 +3732,11 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>SUM(B3:B3)</f>
+        <f>IF('Heure par heure'!D3="","",'Heure par heure'!D3-N('Heure par heure'!D2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>SUM(B3:C3)</f>
         <v/>
       </c>
     </row>
@@ -3618,7 +3750,11 @@
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUM(B4:B4)</f>
+        <f>IF('Heure par heure'!D4="","",'Heure par heure'!D4-N('Heure par heure'!D3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>SUM(B4:C4)</f>
         <v/>
       </c>
     </row>
@@ -3632,7 +3768,11 @@
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>SUM(B5:B5)</f>
+        <f>IF('Heure par heure'!D5="","",'Heure par heure'!D5-N('Heure par heure'!D4))</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>SUM(B5:C5)</f>
         <v/>
       </c>
     </row>
@@ -3646,7 +3786,11 @@
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>SUM(B6:B6)</f>
+        <f>IF('Heure par heure'!D6="","",'Heure par heure'!D6-N('Heure par heure'!D5))</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>SUM(B6:C6)</f>
         <v/>
       </c>
     </row>
@@ -3660,7 +3804,11 @@
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>SUM(B7:B7)</f>
+        <f>IF('Heure par heure'!D7="","",'Heure par heure'!D7-N('Heure par heure'!D6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>SUM(B7:C7)</f>
         <v/>
       </c>
     </row>
@@ -3674,7 +3822,11 @@
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>SUM(B8:B8)</f>
+        <f>IF('Heure par heure'!D8="","",'Heure par heure'!D8-N('Heure par heure'!D7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>SUM(B8:C8)</f>
         <v/>
       </c>
     </row>
@@ -3688,7 +3840,11 @@
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>SUM(B9:B9)</f>
+        <f>IF('Heure par heure'!D9="","",'Heure par heure'!D9-N('Heure par heure'!D8))</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>SUM(B9:C9)</f>
         <v/>
       </c>
     </row>
@@ -3702,7 +3858,11 @@
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>SUM(B10:B10)</f>
+        <f>IF('Heure par heure'!D10="","",'Heure par heure'!D10-N('Heure par heure'!D9))</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>SUM(B10:C10)</f>
         <v/>
       </c>
     </row>
@@ -3716,7 +3876,11 @@
         <v/>
       </c>
       <c r="C11" s="3">
-        <f>SUM(B11:B11)</f>
+        <f>IF('Heure par heure'!D11="","",'Heure par heure'!D11-N('Heure par heure'!D10))</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>SUM(B11:C11)</f>
         <v/>
       </c>
     </row>
@@ -3730,7 +3894,11 @@
         <v/>
       </c>
       <c r="C12" s="3">
-        <f>SUM(B12:B12)</f>
+        <f>IF('Heure par heure'!D12="","",'Heure par heure'!D12-N('Heure par heure'!D11))</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>SUM(B12:C12)</f>
         <v/>
       </c>
     </row>
@@ -3744,7 +3912,11 @@
         <v/>
       </c>
       <c r="C13" s="3">
-        <f>SUM(B13:B13)</f>
+        <f>IF('Heure par heure'!D13="","",'Heure par heure'!D13-N('Heure par heure'!D12))</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>SUM(B13:C13)</f>
         <v/>
       </c>
     </row>
@@ -3758,7 +3930,11 @@
         <v/>
       </c>
       <c r="C14" s="3">
-        <f>SUM(B14:B14)</f>
+        <f>IF('Heure par heure'!D14="","",'Heure par heure'!D14-N('Heure par heure'!D13))</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>SUM(B14:C14)</f>
         <v/>
       </c>
     </row>
@@ -3772,7 +3948,11 @@
         <v/>
       </c>
       <c r="C15" s="3">
-        <f>SUM(B15:B15)</f>
+        <f>IF('Heure par heure'!D15="","",'Heure par heure'!D15-N('Heure par heure'!D14))</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>SUM(B15:C15)</f>
         <v/>
       </c>
     </row>
@@ -3786,7 +3966,11 @@
         <v/>
       </c>
       <c r="C16" s="3">
-        <f>SUM(B16:B16)</f>
+        <f>IF('Heure par heure'!D16="","",'Heure par heure'!D16-N('Heure par heure'!D15))</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>SUM(B16:C16)</f>
         <v/>
       </c>
     </row>
@@ -3800,7 +3984,11 @@
         <v/>
       </c>
       <c r="C17" s="3">
-        <f>SUM(B17:B17)</f>
+        <f>IF('Heure par heure'!D17="","",'Heure par heure'!D17-N('Heure par heure'!D16))</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>SUM(B17:C17)</f>
         <v/>
       </c>
     </row>
@@ -3814,7 +4002,11 @@
         <v/>
       </c>
       <c r="C18" s="3">
-        <f>SUM(B18:B18)</f>
+        <f>IF('Heure par heure'!D18="","",'Heure par heure'!D18-N('Heure par heure'!D17))</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>SUM(B18:C18)</f>
         <v/>
       </c>
     </row>
@@ -3828,7 +4020,11 @@
         <v/>
       </c>
       <c r="C19" s="3">
-        <f>SUM(B19:B19)</f>
+        <f>IF('Heure par heure'!D19="","",'Heure par heure'!D19-N('Heure par heure'!D18))</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>SUM(B19:C19)</f>
         <v/>
       </c>
     </row>
@@ -3842,7 +4038,11 @@
         <v/>
       </c>
       <c r="C20" s="3">
-        <f>SUM(B20:B20)</f>
+        <f>IF('Heure par heure'!D20="","",'Heure par heure'!D20-N('Heure par heure'!D19))</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>SUM(B20:C20)</f>
         <v/>
       </c>
     </row>
@@ -3856,7 +4056,11 @@
         <v/>
       </c>
       <c r="C21" s="3">
-        <f>SUM(B21:B21)</f>
+        <f>IF('Heure par heure'!D21="","",'Heure par heure'!D21-N('Heure par heure'!D20))</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>SUM(B21:C21)</f>
         <v/>
       </c>
     </row>
@@ -3870,7 +4074,11 @@
         <v/>
       </c>
       <c r="C22" s="3">
-        <f>SUM(B22:B22)</f>
+        <f>IF('Heure par heure'!D22="","",'Heure par heure'!D22-N('Heure par heure'!D21))</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>SUM(B22:C22)</f>
         <v/>
       </c>
     </row>
@@ -3884,7 +4092,11 @@
         <v/>
       </c>
       <c r="C23" s="3">
-        <f>SUM(B23:B23)</f>
+        <f>IF('Heure par heure'!D23="","",'Heure par heure'!D23-N('Heure par heure'!D22))</f>
+        <v/>
+      </c>
+      <c r="D23" s="3">
+        <f>SUM(B23:C23)</f>
         <v/>
       </c>
     </row>
@@ -3898,7 +4110,11 @@
         <v/>
       </c>
       <c r="C24" s="3">
-        <f>SUM(B24:B24)</f>
+        <f>IF('Heure par heure'!D24="","",'Heure par heure'!D24-N('Heure par heure'!D23))</f>
+        <v/>
+      </c>
+      <c r="D24" s="3">
+        <f>SUM(B24:C24)</f>
         <v/>
       </c>
     </row>
@@ -3912,7 +4128,11 @@
         <v/>
       </c>
       <c r="C25" s="3">
-        <f>SUM(B25:B25)</f>
+        <f>IF('Heure par heure'!D25="","",'Heure par heure'!D25-N('Heure par heure'!D24))</f>
+        <v/>
+      </c>
+      <c r="D25" s="3">
+        <f>SUM(B25:C25)</f>
         <v/>
       </c>
     </row>
@@ -3926,7 +4146,11 @@
         <v/>
       </c>
       <c r="C26" s="3">
-        <f>SUM(B26:B26)</f>
+        <f>IF('Heure par heure'!D26="","",'Heure par heure'!D26-N('Heure par heure'!D25))</f>
+        <v/>
+      </c>
+      <c r="D26" s="3">
+        <f>SUM(B26:C26)</f>
         <v/>
       </c>
     </row>
@@ -3940,7 +4164,11 @@
         <v/>
       </c>
       <c r="C27" s="3">
-        <f>SUM(B27:B27)</f>
+        <f>IF('Heure par heure'!D27="","",'Heure par heure'!D27-N('Heure par heure'!D26))</f>
+        <v/>
+      </c>
+      <c r="D27" s="3">
+        <f>SUM(B27:C27)</f>
         <v/>
       </c>
     </row>
@@ -3954,7 +4182,11 @@
         <v/>
       </c>
       <c r="C28" s="3">
-        <f>SUM(B28:B28)</f>
+        <f>IF('Heure par heure'!D28="","",'Heure par heure'!D28-N('Heure par heure'!D27))</f>
+        <v/>
+      </c>
+      <c r="D28" s="3">
+        <f>SUM(B28:C28)</f>
         <v/>
       </c>
     </row>
@@ -3968,7 +4200,11 @@
         <v/>
       </c>
       <c r="C29" s="3">
-        <f>SUM(B29:B29)</f>
+        <f>IF('Heure par heure'!D29="","",'Heure par heure'!D29-N('Heure par heure'!D28))</f>
+        <v/>
+      </c>
+      <c r="D29" s="3">
+        <f>SUM(B29:C29)</f>
         <v/>
       </c>
     </row>
@@ -3982,7 +4218,11 @@
         <v/>
       </c>
       <c r="C30" s="3">
-        <f>SUM(B30:B30)</f>
+        <f>IF('Heure par heure'!D30="","",'Heure par heure'!D30-N('Heure par heure'!D29))</f>
+        <v/>
+      </c>
+      <c r="D30" s="3">
+        <f>SUM(B30:C30)</f>
         <v/>
       </c>
     </row>
@@ -3996,7 +4236,11 @@
         <v/>
       </c>
       <c r="C31" s="3">
-        <f>SUM(B31:B31)</f>
+        <f>IF('Heure par heure'!D31="","",'Heure par heure'!D31-N('Heure par heure'!D30))</f>
+        <v/>
+      </c>
+      <c r="D31" s="3">
+        <f>SUM(B31:C31)</f>
         <v/>
       </c>
     </row>
@@ -4010,7 +4254,11 @@
         <v/>
       </c>
       <c r="C32" s="3">
-        <f>SUM(B32:B32)</f>
+        <f>IF('Heure par heure'!D32="","",'Heure par heure'!D32-N('Heure par heure'!D31))</f>
+        <v/>
+      </c>
+      <c r="D32" s="3">
+        <f>SUM(B32:C32)</f>
         <v/>
       </c>
     </row>
@@ -4024,7 +4272,11 @@
         <v/>
       </c>
       <c r="C33" s="3">
-        <f>SUM(B33:B33)</f>
+        <f>IF('Heure par heure'!D33="","",'Heure par heure'!D33-N('Heure par heure'!D32))</f>
+        <v/>
+      </c>
+      <c r="D33" s="3">
+        <f>SUM(B33:C33)</f>
         <v/>
       </c>
     </row>
@@ -4038,7 +4290,11 @@
         <v/>
       </c>
       <c r="C34" s="3">
-        <f>SUM(B34:B34)</f>
+        <f>IF('Heure par heure'!D34="","",'Heure par heure'!D34-N('Heure par heure'!D33))</f>
+        <v/>
+      </c>
+      <c r="D34" s="3">
+        <f>SUM(B34:C34)</f>
         <v/>
       </c>
     </row>
@@ -4052,7 +4308,11 @@
         <v/>
       </c>
       <c r="C35" s="3">
-        <f>SUM(B35:B35)</f>
+        <f>IF('Heure par heure'!D35="","",'Heure par heure'!D35-N('Heure par heure'!D34))</f>
+        <v/>
+      </c>
+      <c r="D35" s="3">
+        <f>SUM(B35:C35)</f>
         <v/>
       </c>
     </row>
@@ -4066,7 +4326,11 @@
         <v/>
       </c>
       <c r="C36" s="3">
-        <f>SUM(B36:B36)</f>
+        <f>IF('Heure par heure'!D36="","",'Heure par heure'!D36-N('Heure par heure'!D35))</f>
+        <v/>
+      </c>
+      <c r="D36" s="3">
+        <f>SUM(B36:C36)</f>
         <v/>
       </c>
     </row>
@@ -4080,7 +4344,11 @@
         <v/>
       </c>
       <c r="C37" s="3">
-        <f>SUM(B37:B37)</f>
+        <f>IF('Heure par heure'!D37="","",'Heure par heure'!D37-N('Heure par heure'!D36))</f>
+        <v/>
+      </c>
+      <c r="D37" s="3">
+        <f>SUM(B37:C37)</f>
         <v/>
       </c>
     </row>
@@ -4094,7 +4362,11 @@
         <v/>
       </c>
       <c r="C38" s="3">
-        <f>SUM(B38:B38)</f>
+        <f>IF('Heure par heure'!D38="","",'Heure par heure'!D38-N('Heure par heure'!D37))</f>
+        <v/>
+      </c>
+      <c r="D38" s="3">
+        <f>SUM(B38:C38)</f>
         <v/>
       </c>
     </row>
@@ -4108,7 +4380,11 @@
         <v/>
       </c>
       <c r="C39" s="3">
-        <f>SUM(B39:B39)</f>
+        <f>IF('Heure par heure'!D39="","",'Heure par heure'!D39-N('Heure par heure'!D38))</f>
+        <v/>
+      </c>
+      <c r="D39" s="3">
+        <f>SUM(B39:C39)</f>
         <v/>
       </c>
     </row>
@@ -4122,7 +4398,29 @@
         <v/>
       </c>
       <c r="C40" s="3">
-        <f>SUM(B40:B40)</f>
+        <f>IF('Heure par heure'!D40="","",'Heure par heure'!D40-N('Heure par heure'!D39))</f>
+        <v/>
+      </c>
+      <c r="D40" s="3">
+        <f>SUM(B40:C40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <f>'Heure par heure'!A41</f>
+        <v/>
+      </c>
+      <c r="B41" s="3">
+        <f>IF('Heure par heure'!C41="","",'Heure par heure'!C41-N('Heure par heure'!C40))</f>
+        <v/>
+      </c>
+      <c r="C41" s="3">
+        <f>IF('Heure par heure'!D41="","",'Heure par heure'!D41-N('Heure par heure'!D40))</f>
+        <v/>
+      </c>
+      <c r="D41" s="3">
+        <f>SUM(B41:C41)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$41</f>
+              <f>'Heure par heure'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$41</f>
+              <f>'Heure par heure'!$D$2:$D$42</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$41</f>
+              <f>'Heure par heure'!$B$2:$B$42</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -585,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$41</f>
+              <f>'Heure par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$41</f>
+              <f>'Heure par heure'!$E$2:$E$42</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -684,12 +684,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$41</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$42</f>
             </numRef>
           </val>
         </ser>
@@ -708,12 +708,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$41</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$41</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$42</f>
             </numRef>
           </val>
         </ser>
@@ -2043,7 +2043,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2065,7 +2065,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2087,7 +2087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2114,7 +2114,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>43</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2962,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3664,6 +3664,26 @@
       </c>
       <c r="E41" s="3">
         <f>SUM(C41:D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 21:00</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E42" s="3">
+        <f>SUM(C42:D42)</f>
         <v/>
       </c>
     </row>
@@ -3679,7 +3699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4421,6 +4441,24 @@
       </c>
       <c r="D41" s="3">
         <f>SUM(B41:C41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <f>'Heure par heure'!A42</f>
+        <v/>
+      </c>
+      <c r="B42" s="3">
+        <f>IF('Heure par heure'!C42="","",'Heure par heure'!C42-N('Heure par heure'!C41))</f>
+        <v/>
+      </c>
+      <c r="C42" s="3">
+        <f>IF('Heure par heure'!D42="","",'Heure par heure'!D42-N('Heure par heure'!D41))</f>
+        <v/>
+      </c>
+      <c r="D42" s="3">
+        <f>SUM(B42:C42)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$42</f>
+              <f>'Heure par heure'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$42</f>
+              <f>'Heure par heure'!$D$2:$D$43</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$42</f>
+              <f>'Heure par heure'!$B$2:$B$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -585,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$42</f>
+              <f>'Heure par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$42</f>
+              <f>'Heure par heure'!$E$2:$E$43</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -684,12 +684,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$42</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$43</f>
             </numRef>
           </val>
         </ser>
@@ -708,12 +708,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$42</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$42</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$43</f>
             </numRef>
           </val>
         </ser>
@@ -2043,7 +2043,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2065,7 +2065,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2087,7 +2087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2114,7 +2114,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2962,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3684,6 +3684,26 @@
       </c>
       <c r="E42" s="3">
         <f>SUM(C42:D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 22:00</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E43" s="3">
+        <f>SUM(C43:D43)</f>
         <v/>
       </c>
     </row>
@@ -3699,7 +3719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4459,6 +4479,24 @@
       </c>
       <c r="D42" s="3">
         <f>SUM(B42:C42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <f>'Heure par heure'!A43</f>
+        <v/>
+      </c>
+      <c r="B43" s="3">
+        <f>IF('Heure par heure'!C43="","",'Heure par heure'!C43-N('Heure par heure'!C42))</f>
+        <v/>
+      </c>
+      <c r="C43" s="3">
+        <f>IF('Heure par heure'!D43="","",'Heure par heure'!D43-N('Heure par heure'!D42))</f>
+        <v/>
+      </c>
+      <c r="D43" s="3">
+        <f>SUM(B43:C43)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$43</f>
+              <f>'Heure par heure'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$43</f>
+              <f>'Heure par heure'!$D$2:$D$44</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$43</f>
+              <f>'Heure par heure'!$B$2:$B$44</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -585,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$43</f>
+              <f>'Heure par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$43</f>
+              <f>'Heure par heure'!$E$2:$E$44</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -684,12 +684,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$43</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$44</f>
             </numRef>
           </val>
         </ser>
@@ -708,12 +708,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$43</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$43</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$44</f>
             </numRef>
           </val>
         </ser>
@@ -2043,7 +2043,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2065,7 +2065,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2087,7 +2087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2114,7 +2114,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2962,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3704,6 +3704,26 @@
       </c>
       <c r="E43" s="3">
         <f>SUM(C43:D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:00</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E44" s="3">
+        <f>SUM(C44:D44)</f>
         <v/>
       </c>
     </row>
@@ -3719,7 +3739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4497,6 +4517,24 @@
       </c>
       <c r="D43" s="3">
         <f>SUM(B43:C43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <f>'Heure par heure'!A44</f>
+        <v/>
+      </c>
+      <c r="B44" s="3">
+        <f>IF('Heure par heure'!C44="","",'Heure par heure'!C44-N('Heure par heure'!C43))</f>
+        <v/>
+      </c>
+      <c r="C44" s="3">
+        <f>IF('Heure par heure'!D44="","",'Heure par heure'!D44-N('Heure par heure'!D43))</f>
+        <v/>
+      </c>
+      <c r="D44" s="3">
+        <f>SUM(B44:C44)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$44</f>
+              <f>'Heure par heure'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$44</f>
+              <f>'Heure par heure'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$44</f>
+              <f>'Heure par heure'!$B$2:$B$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -585,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$44</f>
+              <f>'Heure par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$44</f>
+              <f>'Heure par heure'!$E$2:$E$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -684,12 +684,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$44</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -708,12 +708,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$44</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$44</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$45</f>
             </numRef>
           </val>
         </ser>
@@ -2043,7 +2043,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2065,7 +2065,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2087,7 +2087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2114,7 +2114,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>46</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2962,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3724,6 +3724,26 @@
       </c>
       <c r="E44" s="3">
         <f>SUM(C44:D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 06:00</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E45" s="3">
+        <f>SUM(C45:D45)</f>
         <v/>
       </c>
     </row>
@@ -3739,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4535,6 +4555,24 @@
       </c>
       <c r="D44" s="3">
         <f>SUM(B44:C44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <f>'Heure par heure'!A45</f>
+        <v/>
+      </c>
+      <c r="B45" s="3">
+        <f>IF('Heure par heure'!C45="","",'Heure par heure'!C45-N('Heure par heure'!C44))</f>
+        <v/>
+      </c>
+      <c r="C45" s="3">
+        <f>IF('Heure par heure'!D45="","",'Heure par heure'!D45-N('Heure par heure'!D44))</f>
+        <v/>
+      </c>
+      <c r="D45" s="3">
+        <f>SUM(B45:C45)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$45</f>
+              <f>'Heure par heure'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$45</f>
+              <f>'Heure par heure'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +472,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$45</f>
+              <f>'Heure par heure'!$B$2:$B$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -585,12 +585,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$45</f>
+              <f>'Heure par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$45</f>
+              <f>'Heure par heure'!$E$2:$E$46</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -684,12 +684,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$45</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -708,12 +708,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$45</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$45</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$46</f>
             </numRef>
           </val>
         </ser>
@@ -2043,7 +2043,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2065,7 +2065,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2087,7 +2087,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2114,7 +2114,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>47</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2962,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3744,6 +3744,26 @@
       </c>
       <c r="E45" s="3">
         <f>SUM(C45:D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:00</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E46" s="3">
+        <f>SUM(C46:D46)</f>
         <v/>
       </c>
     </row>
@@ -3759,7 +3779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4573,6 +4593,24 @@
       </c>
       <c r="D45" s="3">
         <f>SUM(B45:C45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <f>'Heure par heure'!A46</f>
+        <v/>
+      </c>
+      <c r="B46" s="3">
+        <f>IF('Heure par heure'!C46="","",'Heure par heure'!C46-N('Heure par heure'!C45))</f>
+        <v/>
+      </c>
+      <c r="C46" s="3">
+        <f>IF('Heure par heure'!D46="","",'Heure par heure'!D46-N('Heure par heure'!D45))</f>
+        <v/>
+      </c>
+      <c r="D46" s="3">
+        <f>SUM(B46:C46)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$46</f>
+              <f>'Heure par heure'!$C$2:$C$47</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,44 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$46</f>
+              <f>'Heure par heure'!$D$2:$D$47</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Heure par heure'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Heure par heure'!$A$2:$A$47</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Heure par heure'!$E$2:$E$47</f>
             </numRef>
           </val>
         </ser>
@@ -472,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$46</f>
+              <f>'Heure par heure'!$B$2:$B$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,7 +592,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Heure par heure'!E1</f>
+              <f>'Heure par heure'!F1</f>
             </strRef>
           </tx>
           <spPr>
@@ -585,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$46</f>
+              <f>'Heure par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$46</f>
+              <f>'Heure par heure'!$F$2:$F$47</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -684,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$46</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -708,12 +740,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$46</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$46</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$47</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vues gagnées par heure'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues gagnées par heure'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -2043,7 +2099,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2065,7 +2121,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2087,7 +2143,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2114,7 +2170,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>48</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -2962,14 +3018,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2995,6 +3052,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>10-28 Un pont tombé par un v</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Vues totales</t>
         </is>
       </c>
@@ -3010,8 +3072,9 @@
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3">
-        <f>SUM(C2:D2)</f>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3">
+        <f>SUM(C2:E2)</f>
         <v/>
       </c>
     </row>
@@ -3026,8 +3089,9 @@
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3">
-        <f>SUM(C3:D3)</f>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3">
+        <f>SUM(C3:E3)</f>
         <v/>
       </c>
     </row>
@@ -3042,8 +3106,9 @@
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3">
-        <f>SUM(C4:D4)</f>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3">
+        <f>SUM(C4:E4)</f>
         <v/>
       </c>
     </row>
@@ -3058,8 +3123,9 @@
       </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3">
-        <f>SUM(C5:D5)</f>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3">
+        <f>SUM(C5:E5)</f>
         <v/>
       </c>
     </row>
@@ -3074,8 +3140,9 @@
       </c>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3">
-        <f>SUM(C6:D6)</f>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3">
+        <f>SUM(C6:E6)</f>
         <v/>
       </c>
     </row>
@@ -3090,8 +3157,9 @@
       </c>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3">
-        <f>SUM(C7:D7)</f>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3">
+        <f>SUM(C7:E7)</f>
         <v/>
       </c>
     </row>
@@ -3106,8 +3174,9 @@
       </c>
       <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3">
-        <f>SUM(C8:D8)</f>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3">
+        <f>SUM(C8:E8)</f>
         <v/>
       </c>
     </row>
@@ -3122,8 +3191,9 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3">
-        <f>SUM(C9:D9)</f>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3">
+        <f>SUM(C9:E9)</f>
         <v/>
       </c>
     </row>
@@ -3138,8 +3208,9 @@
       </c>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3">
-        <f>SUM(C10:D10)</f>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3">
+        <f>SUM(C10:E10)</f>
         <v/>
       </c>
     </row>
@@ -3154,8 +3225,9 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3">
-        <f>SUM(C11:D11)</f>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3">
+        <f>SUM(C11:E11)</f>
         <v/>
       </c>
     </row>
@@ -3170,8 +3242,9 @@
       </c>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3">
-        <f>SUM(C12:D12)</f>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3">
+        <f>SUM(C12:E12)</f>
         <v/>
       </c>
     </row>
@@ -3186,8 +3259,9 @@
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3">
-        <f>SUM(C13:D13)</f>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3">
+        <f>SUM(C13:E13)</f>
         <v/>
       </c>
     </row>
@@ -3202,8 +3276,9 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3">
-        <f>SUM(C14:D14)</f>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3">
+        <f>SUM(C14:E14)</f>
         <v/>
       </c>
     </row>
@@ -3218,8 +3293,9 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3">
-        <f>SUM(C15:D15)</f>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3">
+        <f>SUM(C15:E15)</f>
         <v/>
       </c>
     </row>
@@ -3234,8 +3310,9 @@
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3">
-        <f>SUM(C16:D16)</f>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3">
+        <f>SUM(C16:E16)</f>
         <v/>
       </c>
     </row>
@@ -3250,8 +3327,9 @@
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3">
-        <f>SUM(C17:D17)</f>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3">
+        <f>SUM(C17:E17)</f>
         <v/>
       </c>
     </row>
@@ -3266,8 +3344,9 @@
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3">
-        <f>SUM(C18:D18)</f>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3">
+        <f>SUM(C18:E18)</f>
         <v/>
       </c>
     </row>
@@ -3282,8 +3361,9 @@
       </c>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3">
-        <f>SUM(C19:D19)</f>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3">
+        <f>SUM(C19:E19)</f>
         <v/>
       </c>
     </row>
@@ -3298,8 +3378,9 @@
       </c>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3">
-        <f>SUM(C20:D20)</f>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3">
+        <f>SUM(C20:E20)</f>
         <v/>
       </c>
     </row>
@@ -3314,8 +3395,9 @@
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3">
-        <f>SUM(C21:D21)</f>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3">
+        <f>SUM(C21:E21)</f>
         <v/>
       </c>
     </row>
@@ -3330,8 +3412,9 @@
       </c>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3">
-        <f>SUM(C22:D22)</f>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3">
+        <f>SUM(C22:E22)</f>
         <v/>
       </c>
     </row>
@@ -3346,8 +3429,9 @@
       </c>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3">
-        <f>SUM(C23:D23)</f>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3">
+        <f>SUM(C23:E23)</f>
         <v/>
       </c>
     </row>
@@ -3362,8 +3446,9 @@
       </c>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3">
-        <f>SUM(C24:D24)</f>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3">
+        <f>SUM(C24:E24)</f>
         <v/>
       </c>
     </row>
@@ -3378,8 +3463,9 @@
       </c>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3">
-        <f>SUM(C25:D25)</f>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3">
+        <f>SUM(C25:E25)</f>
         <v/>
       </c>
     </row>
@@ -3394,8 +3480,9 @@
       </c>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3">
-        <f>SUM(C26:D26)</f>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3">
+        <f>SUM(C26:E26)</f>
         <v/>
       </c>
     </row>
@@ -3410,8 +3497,9 @@
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3">
-        <f>SUM(C27:D27)</f>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3">
+        <f>SUM(C27:E27)</f>
         <v/>
       </c>
     </row>
@@ -3426,8 +3514,9 @@
       </c>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3">
-        <f>SUM(C28:D28)</f>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3">
+        <f>SUM(C28:E28)</f>
         <v/>
       </c>
     </row>
@@ -3444,8 +3533,9 @@
         <v>0</v>
       </c>
       <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3">
-        <f>SUM(C29:D29)</f>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3">
+        <f>SUM(C29:E29)</f>
         <v/>
       </c>
     </row>
@@ -3462,8 +3552,9 @@
         <v>28</v>
       </c>
       <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3">
-        <f>SUM(C30:D30)</f>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3">
+        <f>SUM(C30:E30)</f>
         <v/>
       </c>
     </row>
@@ -3480,8 +3571,9 @@
         <v>108</v>
       </c>
       <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3">
-        <f>SUM(C31:D31)</f>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3">
+        <f>SUM(C31:E31)</f>
         <v/>
       </c>
     </row>
@@ -3498,8 +3590,9 @@
         <v>119</v>
       </c>
       <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3">
-        <f>SUM(C32:D32)</f>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3">
+        <f>SUM(C32:E32)</f>
         <v/>
       </c>
     </row>
@@ -3516,8 +3609,9 @@
         <v>119</v>
       </c>
       <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3">
-        <f>SUM(C33:D33)</f>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3">
+        <f>SUM(C33:E33)</f>
         <v/>
       </c>
     </row>
@@ -3534,8 +3628,9 @@
         <v>119</v>
       </c>
       <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3">
-        <f>SUM(C34:D34)</f>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3">
+        <f>SUM(C34:E34)</f>
         <v/>
       </c>
     </row>
@@ -3552,8 +3647,9 @@
         <v>119</v>
       </c>
       <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3">
-        <f>SUM(C35:D35)</f>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3">
+        <f>SUM(C35:E35)</f>
         <v/>
       </c>
     </row>
@@ -3570,8 +3666,9 @@
         <v>119</v>
       </c>
       <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3">
-        <f>SUM(C36:D36)</f>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3">
+        <f>SUM(C36:E36)</f>
         <v/>
       </c>
     </row>
@@ -3588,8 +3685,9 @@
         <v>119</v>
       </c>
       <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3">
-        <f>SUM(C37:D37)</f>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3">
+        <f>SUM(C37:E37)</f>
         <v/>
       </c>
     </row>
@@ -3606,8 +3704,9 @@
         <v>120</v>
       </c>
       <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3">
-        <f>SUM(C38:D38)</f>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3">
+        <f>SUM(C38:E38)</f>
         <v/>
       </c>
     </row>
@@ -3624,8 +3723,9 @@
         <v>120</v>
       </c>
       <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3">
-        <f>SUM(C39:D39)</f>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3">
+        <f>SUM(C39:E39)</f>
         <v/>
       </c>
     </row>
@@ -3642,8 +3742,9 @@
         <v>120</v>
       </c>
       <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3">
-        <f>SUM(C40:D40)</f>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3">
+        <f>SUM(C40:E40)</f>
         <v/>
       </c>
     </row>
@@ -3662,8 +3763,9 @@
       <c r="D41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="3">
-        <f>SUM(C41:D41)</f>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3">
+        <f>SUM(C41:E41)</f>
         <v/>
       </c>
     </row>
@@ -3682,8 +3784,9 @@
       <c r="D42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E42" s="3">
-        <f>SUM(C42:D42)</f>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3">
+        <f>SUM(C42:E42)</f>
         <v/>
       </c>
     </row>
@@ -3702,8 +3805,9 @@
       <c r="D43" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="E43" s="3">
-        <f>SUM(C43:D43)</f>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3">
+        <f>SUM(C43:E43)</f>
         <v/>
       </c>
     </row>
@@ -3722,8 +3826,9 @@
       <c r="D44" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="E44" s="3">
-        <f>SUM(C44:D44)</f>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3">
+        <f>SUM(C44:E44)</f>
         <v/>
       </c>
     </row>
@@ -3742,8 +3847,9 @@
       <c r="D45" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="E45" s="3">
-        <f>SUM(C45:D45)</f>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3">
+        <f>SUM(C45:E45)</f>
         <v/>
       </c>
     </row>
@@ -3762,8 +3868,32 @@
       <c r="D46" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="E46" s="3">
-        <f>SUM(C46:D46)</f>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3">
+        <f>SUM(C46:E46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:00</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <f>SUM(C47:E47)</f>
         <v/>
       </c>
     </row>
@@ -3779,13 +3909,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3806,6 +3937,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>10-28 Un pont tombé par un v</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Total de l'heure</t>
         </is>
       </c>
@@ -3817,8 +3953,9 @@
       </c>
       <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3">
-        <f>SUM(B2:C2)</f>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3">
+        <f>SUM(B2:D2)</f>
         <v/>
       </c>
     </row>
@@ -3836,7 +3973,11 @@
         <v/>
       </c>
       <c r="D3" s="3">
-        <f>SUM(B3:C3)</f>
+        <f>IF('Heure par heure'!E3="","",'Heure par heure'!E3-N('Heure par heure'!E2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM(B3:D3)</f>
         <v/>
       </c>
     </row>
@@ -3854,7 +3995,11 @@
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>SUM(B4:C4)</f>
+        <f>IF('Heure par heure'!E4="","",'Heure par heure'!E4-N('Heure par heure'!E3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(B4:D4)</f>
         <v/>
       </c>
     </row>
@@ -3872,7 +4017,11 @@
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>SUM(B5:C5)</f>
+        <f>IF('Heure par heure'!E5="","",'Heure par heure'!E5-N('Heure par heure'!E4))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>SUM(B5:D5)</f>
         <v/>
       </c>
     </row>
@@ -3890,7 +4039,11 @@
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>SUM(B6:C6)</f>
+        <f>IF('Heure par heure'!E6="","",'Heure par heure'!E6-N('Heure par heure'!E5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(B6:D6)</f>
         <v/>
       </c>
     </row>
@@ -3908,7 +4061,11 @@
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>SUM(B7:C7)</f>
+        <f>IF('Heure par heure'!E7="","",'Heure par heure'!E7-N('Heure par heure'!E6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>SUM(B7:D7)</f>
         <v/>
       </c>
     </row>
@@ -3926,7 +4083,11 @@
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>SUM(B8:C8)</f>
+        <f>IF('Heure par heure'!E8="","",'Heure par heure'!E8-N('Heure par heure'!E7))</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM(B8:D8)</f>
         <v/>
       </c>
     </row>
@@ -3944,7 +4105,11 @@
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>SUM(B9:C9)</f>
+        <f>IF('Heure par heure'!E9="","",'Heure par heure'!E9-N('Heure par heure'!E8))</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM(B9:D9)</f>
         <v/>
       </c>
     </row>
@@ -3962,7 +4127,11 @@
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>SUM(B10:C10)</f>
+        <f>IF('Heure par heure'!E10="","",'Heure par heure'!E10-N('Heure par heure'!E9))</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>SUM(B10:D10)</f>
         <v/>
       </c>
     </row>
@@ -3980,7 +4149,11 @@
         <v/>
       </c>
       <c r="D11" s="3">
-        <f>SUM(B11:C11)</f>
+        <f>IF('Heure par heure'!E11="","",'Heure par heure'!E11-N('Heure par heure'!E10))</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>SUM(B11:D11)</f>
         <v/>
       </c>
     </row>
@@ -3998,7 +4171,11 @@
         <v/>
       </c>
       <c r="D12" s="3">
-        <f>SUM(B12:C12)</f>
+        <f>IF('Heure par heure'!E12="","",'Heure par heure'!E12-N('Heure par heure'!E11))</f>
+        <v/>
+      </c>
+      <c r="E12" s="3">
+        <f>SUM(B12:D12)</f>
         <v/>
       </c>
     </row>
@@ -4016,7 +4193,11 @@
         <v/>
       </c>
       <c r="D13" s="3">
-        <f>SUM(B13:C13)</f>
+        <f>IF('Heure par heure'!E13="","",'Heure par heure'!E13-N('Heure par heure'!E12))</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>SUM(B13:D13)</f>
         <v/>
       </c>
     </row>
@@ -4034,7 +4215,11 @@
         <v/>
       </c>
       <c r="D14" s="3">
-        <f>SUM(B14:C14)</f>
+        <f>IF('Heure par heure'!E14="","",'Heure par heure'!E14-N('Heure par heure'!E13))</f>
+        <v/>
+      </c>
+      <c r="E14" s="3">
+        <f>SUM(B14:D14)</f>
         <v/>
       </c>
     </row>
@@ -4052,7 +4237,11 @@
         <v/>
       </c>
       <c r="D15" s="3">
-        <f>SUM(B15:C15)</f>
+        <f>IF('Heure par heure'!E15="","",'Heure par heure'!E15-N('Heure par heure'!E14))</f>
+        <v/>
+      </c>
+      <c r="E15" s="3">
+        <f>SUM(B15:D15)</f>
         <v/>
       </c>
     </row>
@@ -4070,7 +4259,11 @@
         <v/>
       </c>
       <c r="D16" s="3">
-        <f>SUM(B16:C16)</f>
+        <f>IF('Heure par heure'!E16="","",'Heure par heure'!E16-N('Heure par heure'!E15))</f>
+        <v/>
+      </c>
+      <c r="E16" s="3">
+        <f>SUM(B16:D16)</f>
         <v/>
       </c>
     </row>
@@ -4088,7 +4281,11 @@
         <v/>
       </c>
       <c r="D17" s="3">
-        <f>SUM(B17:C17)</f>
+        <f>IF('Heure par heure'!E17="","",'Heure par heure'!E17-N('Heure par heure'!E16))</f>
+        <v/>
+      </c>
+      <c r="E17" s="3">
+        <f>SUM(B17:D17)</f>
         <v/>
       </c>
     </row>
@@ -4106,7 +4303,11 @@
         <v/>
       </c>
       <c r="D18" s="3">
-        <f>SUM(B18:C18)</f>
+        <f>IF('Heure par heure'!E18="","",'Heure par heure'!E18-N('Heure par heure'!E17))</f>
+        <v/>
+      </c>
+      <c r="E18" s="3">
+        <f>SUM(B18:D18)</f>
         <v/>
       </c>
     </row>
@@ -4124,7 +4325,11 @@
         <v/>
       </c>
       <c r="D19" s="3">
-        <f>SUM(B19:C19)</f>
+        <f>IF('Heure par heure'!E19="","",'Heure par heure'!E19-N('Heure par heure'!E18))</f>
+        <v/>
+      </c>
+      <c r="E19" s="3">
+        <f>SUM(B19:D19)</f>
         <v/>
       </c>
     </row>
@@ -4142,7 +4347,11 @@
         <v/>
       </c>
       <c r="D20" s="3">
-        <f>SUM(B20:C20)</f>
+        <f>IF('Heure par heure'!E20="","",'Heure par heure'!E20-N('Heure par heure'!E19))</f>
+        <v/>
+      </c>
+      <c r="E20" s="3">
+        <f>SUM(B20:D20)</f>
         <v/>
       </c>
     </row>
@@ -4160,7 +4369,11 @@
         <v/>
       </c>
       <c r="D21" s="3">
-        <f>SUM(B21:C21)</f>
+        <f>IF('Heure par heure'!E21="","",'Heure par heure'!E21-N('Heure par heure'!E20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>SUM(B21:D21)</f>
         <v/>
       </c>
     </row>
@@ -4178,7 +4391,11 @@
         <v/>
       </c>
       <c r="D22" s="3">
-        <f>SUM(B22:C22)</f>
+        <f>IF('Heure par heure'!E22="","",'Heure par heure'!E22-N('Heure par heure'!E21))</f>
+        <v/>
+      </c>
+      <c r="E22" s="3">
+        <f>SUM(B22:D22)</f>
         <v/>
       </c>
     </row>
@@ -4196,7 +4413,11 @@
         <v/>
       </c>
       <c r="D23" s="3">
-        <f>SUM(B23:C23)</f>
+        <f>IF('Heure par heure'!E23="","",'Heure par heure'!E23-N('Heure par heure'!E22))</f>
+        <v/>
+      </c>
+      <c r="E23" s="3">
+        <f>SUM(B23:D23)</f>
         <v/>
       </c>
     </row>
@@ -4214,7 +4435,11 @@
         <v/>
       </c>
       <c r="D24" s="3">
-        <f>SUM(B24:C24)</f>
+        <f>IF('Heure par heure'!E24="","",'Heure par heure'!E24-N('Heure par heure'!E23))</f>
+        <v/>
+      </c>
+      <c r="E24" s="3">
+        <f>SUM(B24:D24)</f>
         <v/>
       </c>
     </row>
@@ -4232,7 +4457,11 @@
         <v/>
       </c>
       <c r="D25" s="3">
-        <f>SUM(B25:C25)</f>
+        <f>IF('Heure par heure'!E25="","",'Heure par heure'!E25-N('Heure par heure'!E24))</f>
+        <v/>
+      </c>
+      <c r="E25" s="3">
+        <f>SUM(B25:D25)</f>
         <v/>
       </c>
     </row>
@@ -4250,7 +4479,11 @@
         <v/>
       </c>
       <c r="D26" s="3">
-        <f>SUM(B26:C26)</f>
+        <f>IF('Heure par heure'!E26="","",'Heure par heure'!E26-N('Heure par heure'!E25))</f>
+        <v/>
+      </c>
+      <c r="E26" s="3">
+        <f>SUM(B26:D26)</f>
         <v/>
       </c>
     </row>
@@ -4268,7 +4501,11 @@
         <v/>
       </c>
       <c r="D27" s="3">
-        <f>SUM(B27:C27)</f>
+        <f>IF('Heure par heure'!E27="","",'Heure par heure'!E27-N('Heure par heure'!E26))</f>
+        <v/>
+      </c>
+      <c r="E27" s="3">
+        <f>SUM(B27:D27)</f>
         <v/>
       </c>
     </row>
@@ -4286,7 +4523,11 @@
         <v/>
       </c>
       <c r="D28" s="3">
-        <f>SUM(B28:C28)</f>
+        <f>IF('Heure par heure'!E28="","",'Heure par heure'!E28-N('Heure par heure'!E27))</f>
+        <v/>
+      </c>
+      <c r="E28" s="3">
+        <f>SUM(B28:D28)</f>
         <v/>
       </c>
     </row>
@@ -4304,7 +4545,11 @@
         <v/>
       </c>
       <c r="D29" s="3">
-        <f>SUM(B29:C29)</f>
+        <f>IF('Heure par heure'!E29="","",'Heure par heure'!E29-N('Heure par heure'!E28))</f>
+        <v/>
+      </c>
+      <c r="E29" s="3">
+        <f>SUM(B29:D29)</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4567,11 @@
         <v/>
       </c>
       <c r="D30" s="3">
-        <f>SUM(B30:C30)</f>
+        <f>IF('Heure par heure'!E30="","",'Heure par heure'!E30-N('Heure par heure'!E29))</f>
+        <v/>
+      </c>
+      <c r="E30" s="3">
+        <f>SUM(B30:D30)</f>
         <v/>
       </c>
     </row>
@@ -4340,7 +4589,11 @@
         <v/>
       </c>
       <c r="D31" s="3">
-        <f>SUM(B31:C31)</f>
+        <f>IF('Heure par heure'!E31="","",'Heure par heure'!E31-N('Heure par heure'!E30))</f>
+        <v/>
+      </c>
+      <c r="E31" s="3">
+        <f>SUM(B31:D31)</f>
         <v/>
       </c>
     </row>
@@ -4358,7 +4611,11 @@
         <v/>
       </c>
       <c r="D32" s="3">
-        <f>SUM(B32:C32)</f>
+        <f>IF('Heure par heure'!E32="","",'Heure par heure'!E32-N('Heure par heure'!E31))</f>
+        <v/>
+      </c>
+      <c r="E32" s="3">
+        <f>SUM(B32:D32)</f>
         <v/>
       </c>
     </row>
@@ -4376,7 +4633,11 @@
         <v/>
       </c>
       <c r="D33" s="3">
-        <f>SUM(B33:C33)</f>
+        <f>IF('Heure par heure'!E33="","",'Heure par heure'!E33-N('Heure par heure'!E32))</f>
+        <v/>
+      </c>
+      <c r="E33" s="3">
+        <f>SUM(B33:D33)</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4655,11 @@
         <v/>
       </c>
       <c r="D34" s="3">
-        <f>SUM(B34:C34)</f>
+        <f>IF('Heure par heure'!E34="","",'Heure par heure'!E34-N('Heure par heure'!E33))</f>
+        <v/>
+      </c>
+      <c r="E34" s="3">
+        <f>SUM(B34:D34)</f>
         <v/>
       </c>
     </row>
@@ -4412,7 +4677,11 @@
         <v/>
       </c>
       <c r="D35" s="3">
-        <f>SUM(B35:C35)</f>
+        <f>IF('Heure par heure'!E35="","",'Heure par heure'!E35-N('Heure par heure'!E34))</f>
+        <v/>
+      </c>
+      <c r="E35" s="3">
+        <f>SUM(B35:D35)</f>
         <v/>
       </c>
     </row>
@@ -4430,7 +4699,11 @@
         <v/>
       </c>
       <c r="D36" s="3">
-        <f>SUM(B36:C36)</f>
+        <f>IF('Heure par heure'!E36="","",'Heure par heure'!E36-N('Heure par heure'!E35))</f>
+        <v/>
+      </c>
+      <c r="E36" s="3">
+        <f>SUM(B36:D36)</f>
         <v/>
       </c>
     </row>
@@ -4448,7 +4721,11 @@
         <v/>
       </c>
       <c r="D37" s="3">
-        <f>SUM(B37:C37)</f>
+        <f>IF('Heure par heure'!E37="","",'Heure par heure'!E37-N('Heure par heure'!E36))</f>
+        <v/>
+      </c>
+      <c r="E37" s="3">
+        <f>SUM(B37:D37)</f>
         <v/>
       </c>
     </row>
@@ -4466,7 +4743,11 @@
         <v/>
       </c>
       <c r="D38" s="3">
-        <f>SUM(B38:C38)</f>
+        <f>IF('Heure par heure'!E38="","",'Heure par heure'!E38-N('Heure par heure'!E37))</f>
+        <v/>
+      </c>
+      <c r="E38" s="3">
+        <f>SUM(B38:D38)</f>
         <v/>
       </c>
     </row>
@@ -4484,7 +4765,11 @@
         <v/>
       </c>
       <c r="D39" s="3">
-        <f>SUM(B39:C39)</f>
+        <f>IF('Heure par heure'!E39="","",'Heure par heure'!E39-N('Heure par heure'!E38))</f>
+        <v/>
+      </c>
+      <c r="E39" s="3">
+        <f>SUM(B39:D39)</f>
         <v/>
       </c>
     </row>
@@ -4502,7 +4787,11 @@
         <v/>
       </c>
       <c r="D40" s="3">
-        <f>SUM(B40:C40)</f>
+        <f>IF('Heure par heure'!E40="","",'Heure par heure'!E40-N('Heure par heure'!E39))</f>
+        <v/>
+      </c>
+      <c r="E40" s="3">
+        <f>SUM(B40:D40)</f>
         <v/>
       </c>
     </row>
@@ -4520,7 +4809,11 @@
         <v/>
       </c>
       <c r="D41" s="3">
-        <f>SUM(B41:C41)</f>
+        <f>IF('Heure par heure'!E41="","",'Heure par heure'!E41-N('Heure par heure'!E40))</f>
+        <v/>
+      </c>
+      <c r="E41" s="3">
+        <f>SUM(B41:D41)</f>
         <v/>
       </c>
     </row>
@@ -4538,7 +4831,11 @@
         <v/>
       </c>
       <c r="D42" s="3">
-        <f>SUM(B42:C42)</f>
+        <f>IF('Heure par heure'!E42="","",'Heure par heure'!E42-N('Heure par heure'!E41))</f>
+        <v/>
+      </c>
+      <c r="E42" s="3">
+        <f>SUM(B42:D42)</f>
         <v/>
       </c>
     </row>
@@ -4556,7 +4853,11 @@
         <v/>
       </c>
       <c r="D43" s="3">
-        <f>SUM(B43:C43)</f>
+        <f>IF('Heure par heure'!E43="","",'Heure par heure'!E43-N('Heure par heure'!E42))</f>
+        <v/>
+      </c>
+      <c r="E43" s="3">
+        <f>SUM(B43:D43)</f>
         <v/>
       </c>
     </row>
@@ -4574,7 +4875,11 @@
         <v/>
       </c>
       <c r="D44" s="3">
-        <f>SUM(B44:C44)</f>
+        <f>IF('Heure par heure'!E44="","",'Heure par heure'!E44-N('Heure par heure'!E43))</f>
+        <v/>
+      </c>
+      <c r="E44" s="3">
+        <f>SUM(B44:D44)</f>
         <v/>
       </c>
     </row>
@@ -4592,7 +4897,11 @@
         <v/>
       </c>
       <c r="D45" s="3">
-        <f>SUM(B45:C45)</f>
+        <f>IF('Heure par heure'!E45="","",'Heure par heure'!E45-N('Heure par heure'!E44))</f>
+        <v/>
+      </c>
+      <c r="E45" s="3">
+        <f>SUM(B45:D45)</f>
         <v/>
       </c>
     </row>
@@ -4610,7 +4919,33 @@
         <v/>
       </c>
       <c r="D46" s="3">
-        <f>SUM(B46:C46)</f>
+        <f>IF('Heure par heure'!E46="","",'Heure par heure'!E46-N('Heure par heure'!E45))</f>
+        <v/>
+      </c>
+      <c r="E46" s="3">
+        <f>SUM(B46:D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <f>'Heure par heure'!A47</f>
+        <v/>
+      </c>
+      <c r="B47" s="3">
+        <f>IF('Heure par heure'!C47="","",'Heure par heure'!C47-N('Heure par heure'!C46))</f>
+        <v/>
+      </c>
+      <c r="C47" s="3">
+        <f>IF('Heure par heure'!D47="","",'Heure par heure'!D47-N('Heure par heure'!D46))</f>
+        <v/>
+      </c>
+      <c r="D47" s="3">
+        <f>IF('Heure par heure'!E47="","",'Heure par heure'!E47-N('Heure par heure'!E46))</f>
+        <v/>
+      </c>
+      <c r="E47" s="3">
+        <f>SUM(B47:D47)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$4</f>
+              <f>'Jour par jour'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -852,12 +852,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Stories'!$A$2</f>
+              <f>'Stories'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Stories'!$B$2</f>
+              <f>'Stories'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -954,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$4</f>
+              <f>'Jour par jour'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -981,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$4</f>
+              <f>'Jour par jour'!$L$2:$L$5</f>
             </numRef>
           </val>
         </ser>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$4</f>
+              <f>'Jour par jour'!$F$2:$F$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$4</f>
+              <f>'Jour par jour'!$H$2:$H$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1236,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$4</f>
+              <f>'Jour par jour'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$4</f>
+              <f>'Jour par jour'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -1338,12 +1338,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$D$2</f>
+              <f>'Vidéos'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -1440,12 +1440,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$F$2</f>
+              <f>'Vidéos'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -1467,12 +1467,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$G$2</f>
+              <f>'Vidéos'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -1494,12 +1494,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$H$2</f>
+              <f>'Vidéos'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1521,12 +1521,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$I$2</f>
+              <f>'Vidéos'!$I$2:$I$4</f>
             </numRef>
           </val>
         </ser>
@@ -1623,12 +1623,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vidéos'!$B$2</f>
+              <f>'Vidéos'!$B$2:$B$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vidéos'!$K$2</f>
+              <f>'Vidéos'!$K$2:$K$4</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1729,76 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$4</f>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$4</f>
+              <f>'Évolution par vidéo'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$C$2:$C$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Évolution par vidéo'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Évolution par vidéo'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1827,12 +1891,60 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$4</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$4</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$C$2:$C$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Vues du jour par vidéo'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Vues du jour par vidéo'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -1974,7 +2086,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -1996,7 +2108,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2018,7 +2130,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>20</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2045,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2072,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2507,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2727,6 +2839,51 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <f>IF(ROW()=2,"",B5-B4)</f>
+        <v/>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="E5" s="3">
+        <f>IF(ROW()=2,D5,D5-D4)</f>
+        <v/>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -2739,7 +2896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2835,10 +2992,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -2861,15 +3018,109 @@
       </c>
       <c r="L2" s="6">
         <f>IFERROR(D2/E2,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:19</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pourquoi un avion de 575 t ne tombe-t-il pas </t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <f>IFERROR((F3+G3+H3+I3)/IF(E3&gt;0,E3,D3),0)</f>
+        <v/>
+      </c>
+      <c r="L3" s="6">
+        <f>IFERROR(D3/E3,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 07:52</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Un pont tombé par un vent de 64 km/h : Tacoma</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <f>IFERROR((F4+G4+H4+I4)/IF(E4&gt;0,E4,D4),0)</f>
+        <v/>
+      </c>
+      <c r="L4" s="6">
+        <f>IFERROR(D4/E4,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2879,11 +3130,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2897,6 +3150,16 @@
           <t>Comment ce robot canard tien</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pourquoi un avion de 575 t n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Un pont tombé par un vent de</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2905,6 +3168,8 @@
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2913,6 +3178,8 @@
         </is>
       </c>
       <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2922,6 +3189,24 @@
       </c>
       <c r="B4" s="3" t="n">
         <v>119</v>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2936,12 +3221,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2957,6 +3244,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Pourquoi un avion de 575 t n</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Un pont tombé par un vent de</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Total du jour</t>
         </is>
       </c>
@@ -2972,7 +3269,15 @@
         <v/>
       </c>
       <c r="C2" s="3">
-        <f>SUM(B2:B2)</f>
+        <f>IF('Évolution par vidéo'!C2="","",'Évolution par vidéo'!C2)</f>
+        <v/>
+      </c>
+      <c r="D2" s="3">
+        <f>IF('Évolution par vidéo'!D2="","",'Évolution par vidéo'!D2)</f>
+        <v/>
+      </c>
+      <c r="E2" s="3">
+        <f>SUM(B2:D2)</f>
         <v/>
       </c>
     </row>
@@ -2987,7 +3292,15 @@
         <v/>
       </c>
       <c r="C3" s="3">
-        <f>SUM(B3:B3)</f>
+        <f>IF('Évolution par vidéo'!C3="","",'Évolution par vidéo'!C3-N('Évolution par vidéo'!C2))</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>IF('Évolution par vidéo'!D3="","",'Évolution par vidéo'!D3-N('Évolution par vidéo'!D2))</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM(B3:D3)</f>
         <v/>
       </c>
     </row>
@@ -3002,7 +3315,38 @@
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUM(B4:B4)</f>
+        <f>IF('Évolution par vidéo'!C4="","",'Évolution par vidéo'!C4-N('Évolution par vidéo'!C3))</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>IF('Évolution par vidéo'!D4="","",'Évolution par vidéo'!D4-N('Évolution par vidéo'!D3))</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM(B4:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>IF('Évolution par vidéo'!B5="","",'Évolution par vidéo'!B5-N('Évolution par vidéo'!B4))</f>
+        <v/>
+      </c>
+      <c r="C5" s="3">
+        <f>IF('Évolution par vidéo'!C5="","",'Évolution par vidéo'!C5-N('Évolution par vidéo'!C4))</f>
+        <v/>
+      </c>
+      <c r="D5" s="3">
+        <f>IF('Évolution par vidéo'!D5="","",'Évolution par vidéo'!D5-N('Évolution par vidéo'!D4))</f>
+        <v/>
+      </c>
+      <c r="E5" s="3">
+        <f>SUM(B5:D5)</f>
         <v/>
       </c>
     </row>
@@ -4961,7 +5305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5055,12 +5399,114 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:13</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27 19:20</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 05:35</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ouvrir</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$47</f>
+              <f>'Heure par heure'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$47</f>
+              <f>'Heure par heure'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$47</f>
+              <f>'Heure par heure'!$E$2:$E$48</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$47</f>
+              <f>'Heure par heure'!$B$2:$B$48</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$47</f>
+              <f>'Heure par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$47</f>
+              <f>'Heure par heure'!$F$2:$F$48</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$47</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$47</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$48</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$47</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$47</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>49</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4241,6 +4241,29 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F48" s="3">
+        <f>SUM(C48:E48)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4253,7 +4276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5290,6 +5313,28 @@
       </c>
       <c r="E47" s="3">
         <f>SUM(B47:D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <f>'Heure par heure'!A48</f>
+        <v/>
+      </c>
+      <c r="B48" s="3">
+        <f>IF('Heure par heure'!C48="","",'Heure par heure'!C48-N('Heure par heure'!C47))</f>
+        <v/>
+      </c>
+      <c r="C48" s="3">
+        <f>IF('Heure par heure'!D48="","",'Heure par heure'!D48-N('Heure par heure'!D47))</f>
+        <v/>
+      </c>
+      <c r="D48" s="3">
+        <f>IF('Heure par heure'!E48="","",'Heure par heure'!E48-N('Heure par heure'!E47))</f>
+        <v/>
+      </c>
+      <c r="E48" s="3">
+        <f>SUM(B48:D48)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$48</f>
+              <f>'Heure par heure'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$48</f>
+              <f>'Heure par heure'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$48</f>
+              <f>'Heure par heure'!$E$2:$E$49</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$48</f>
+              <f>'Heure par heure'!$B$2:$B$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$48</f>
+              <f>'Heure par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$48</f>
+              <f>'Heure par heure'!$F$2:$F$49</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$48</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$48</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$49</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$48</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$48</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>50</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4264,6 +4264,29 @@
         <v/>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:00</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="F49" s="3">
+        <f>SUM(C49:E49)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4276,7 +4299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5335,6 +5358,28 @@
       </c>
       <c r="E48" s="3">
         <f>SUM(B48:D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <f>'Heure par heure'!A49</f>
+        <v/>
+      </c>
+      <c r="B49" s="3">
+        <f>IF('Heure par heure'!C49="","",'Heure par heure'!C49-N('Heure par heure'!C48))</f>
+        <v/>
+      </c>
+      <c r="C49" s="3">
+        <f>IF('Heure par heure'!D49="","",'Heure par heure'!D49-N('Heure par heure'!D48))</f>
+        <v/>
+      </c>
+      <c r="D49" s="3">
+        <f>IF('Heure par heure'!E49="","",'Heure par heure'!E49-N('Heure par heure'!E48))</f>
+        <v/>
+      </c>
+      <c r="E49" s="3">
+        <f>SUM(B49:D49)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$49</f>
+              <f>'Heure par heure'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$49</f>
+              <f>'Heure par heure'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$49</f>
+              <f>'Heure par heure'!$E$2:$E$50</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$49</f>
+              <f>'Heure par heure'!$B$2:$B$50</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$49</f>
+              <f>'Heure par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$49</f>
+              <f>'Heure par heure'!$F$2:$F$50</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$49</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$49</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$50</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$49</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$49</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4287,6 +4287,29 @@
         <v/>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="F50" s="3">
+        <f>SUM(C50:E50)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4299,7 +4322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5380,6 +5403,28 @@
       </c>
       <c r="E49" s="3">
         <f>SUM(B49:D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <f>'Heure par heure'!A50</f>
+        <v/>
+      </c>
+      <c r="B50" s="3">
+        <f>IF('Heure par heure'!C50="","",'Heure par heure'!C50-N('Heure par heure'!C49))</f>
+        <v/>
+      </c>
+      <c r="C50" s="3">
+        <f>IF('Heure par heure'!D50="","",'Heure par heure'!D50-N('Heure par heure'!D49))</f>
+        <v/>
+      </c>
+      <c r="D50" s="3">
+        <f>IF('Heure par heure'!E50="","",'Heure par heure'!E50-N('Heure par heure'!E49))</f>
+        <v/>
+      </c>
+      <c r="E50" s="3">
+        <f>SUM(B50:D50)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$50</f>
+              <f>'Heure par heure'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$50</f>
+              <f>'Heure par heure'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$50</f>
+              <f>'Heure par heure'!$E$2:$E$51</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$50</f>
+              <f>'Heure par heure'!$B$2:$B$51</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$50</f>
+              <f>'Heure par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$50</f>
+              <f>'Heure par heure'!$F$2:$F$51</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$50</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$50</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$51</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$50</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$50</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4310,6 +4310,29 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:00</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F51" s="3">
+        <f>SUM(C51:E51)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4322,7 +4345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5425,6 +5448,28 @@
       </c>
       <c r="E50" s="3">
         <f>SUM(B50:D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <f>'Heure par heure'!A51</f>
+        <v/>
+      </c>
+      <c r="B51" s="3">
+        <f>IF('Heure par heure'!C51="","",'Heure par heure'!C51-N('Heure par heure'!C50))</f>
+        <v/>
+      </c>
+      <c r="C51" s="3">
+        <f>IF('Heure par heure'!D51="","",'Heure par heure'!D51-N('Heure par heure'!D50))</f>
+        <v/>
+      </c>
+      <c r="D51" s="3">
+        <f>IF('Heure par heure'!E51="","",'Heure par heure'!E51-N('Heure par heure'!E50))</f>
+        <v/>
+      </c>
+      <c r="E51" s="3">
+        <f>SUM(B51:D51)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$51</f>
+              <f>'Heure par heure'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$51</f>
+              <f>'Heure par heure'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$51</f>
+              <f>'Heure par heure'!$E$2:$E$52</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$51</f>
+              <f>'Heure par heure'!$B$2:$B$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$51</f>
+              <f>'Heure par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$51</f>
+              <f>'Heure par heure'!$F$2:$F$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$51</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$51</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$52</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$51</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$51</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4333,6 +4333,29 @@
         <v/>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:00</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F52" s="3">
+        <f>SUM(C52:E52)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4345,7 +4368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5470,6 +5493,28 @@
       </c>
       <c r="E51" s="3">
         <f>SUM(B51:D51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <f>'Heure par heure'!A52</f>
+        <v/>
+      </c>
+      <c r="B52" s="3">
+        <f>IF('Heure par heure'!C52="","",'Heure par heure'!C52-N('Heure par heure'!C51))</f>
+        <v/>
+      </c>
+      <c r="C52" s="3">
+        <f>IF('Heure par heure'!D52="","",'Heure par heure'!D52-N('Heure par heure'!D51))</f>
+        <v/>
+      </c>
+      <c r="D52" s="3">
+        <f>IF('Heure par heure'!E52="","",'Heure par heure'!E52-N('Heure par heure'!E51))</f>
+        <v/>
+      </c>
+      <c r="E52" s="3">
+        <f>SUM(B52:D52)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$52</f>
+              <f>'Heure par heure'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$52</f>
+              <f>'Heure par heure'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$52</f>
+              <f>'Heure par heure'!$E$2:$E$53</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$52</f>
+              <f>'Heure par heure'!$B$2:$B$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$52</f>
+              <f>'Heure par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$52</f>
+              <f>'Heure par heure'!$F$2:$F$53</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$52</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$52</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$53</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$52</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$52</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>54</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4356,6 +4356,29 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:00</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F53" s="3">
+        <f>SUM(C53:E53)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4368,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5515,6 +5538,28 @@
       </c>
       <c r="E52" s="3">
         <f>SUM(B52:D52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <f>'Heure par heure'!A53</f>
+        <v/>
+      </c>
+      <c r="B53" s="3">
+        <f>IF('Heure par heure'!C53="","",'Heure par heure'!C53-N('Heure par heure'!C52))</f>
+        <v/>
+      </c>
+      <c r="C53" s="3">
+        <f>IF('Heure par heure'!D53="","",'Heure par heure'!D53-N('Heure par heure'!D52))</f>
+        <v/>
+      </c>
+      <c r="D53" s="3">
+        <f>IF('Heure par heure'!E53="","",'Heure par heure'!E53-N('Heure par heure'!E52))</f>
+        <v/>
+      </c>
+      <c r="E53" s="3">
+        <f>SUM(B53:D53)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$53</f>
+              <f>'Heure par heure'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$53</f>
+              <f>'Heure par heure'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$53</f>
+              <f>'Heure par heure'!$E$2:$E$54</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$53</f>
+              <f>'Heure par heure'!$B$2:$B$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$53</f>
+              <f>'Heure par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$53</f>
+              <f>'Heure par heure'!$F$2:$F$54</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$53</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$53</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$54</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$53</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$53</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>55</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4379,6 +4379,29 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:00</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F54" s="3">
+        <f>SUM(C54:E54)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4391,7 +4414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5560,6 +5583,28 @@
       </c>
       <c r="E53" s="3">
         <f>SUM(B53:D53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <f>'Heure par heure'!A54</f>
+        <v/>
+      </c>
+      <c r="B54" s="3">
+        <f>IF('Heure par heure'!C54="","",'Heure par heure'!C54-N('Heure par heure'!C53))</f>
+        <v/>
+      </c>
+      <c r="C54" s="3">
+        <f>IF('Heure par heure'!D54="","",'Heure par heure'!D54-N('Heure par heure'!D53))</f>
+        <v/>
+      </c>
+      <c r="D54" s="3">
+        <f>IF('Heure par heure'!E54="","",'Heure par heure'!E54-N('Heure par heure'!E53))</f>
+        <v/>
+      </c>
+      <c r="E54" s="3">
+        <f>SUM(B54:D54)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -2853,17 +2853,17 @@
         <v/>
       </c>
       <c r="D5" s="3" t="n">
-        <v>221</v>
+        <v>337</v>
       </c>
       <c r="E5" s="3">
         <f>IF(ROW()=2,D5,D5-D4)</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n">
-        <v>211</v>
+        <v>313</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>101</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$54</f>
+              <f>'Heure par heure'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$54</f>
+              <f>'Heure par heure'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$54</f>
+              <f>'Heure par heure'!$E$2:$E$55</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$54</f>
+              <f>'Heure par heure'!$B$2:$B$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$54</f>
+              <f>'Heure par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$54</f>
+              <f>'Heure par heure'!$F$2:$F$55</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$54</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$54</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$55</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$54</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$54</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4402,6 +4402,29 @@
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:00</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F55" s="3">
+        <f>SUM(C55:E55)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4414,7 +4437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5605,6 +5628,28 @@
       </c>
       <c r="E54" s="3">
         <f>SUM(B54:D54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <f>'Heure par heure'!A55</f>
+        <v/>
+      </c>
+      <c r="B55" s="3">
+        <f>IF('Heure par heure'!C55="","",'Heure par heure'!C55-N('Heure par heure'!C54))</f>
+        <v/>
+      </c>
+      <c r="C55" s="3">
+        <f>IF('Heure par heure'!D55="","",'Heure par heure'!D55-N('Heure par heure'!D54))</f>
+        <v/>
+      </c>
+      <c r="D55" s="3">
+        <f>IF('Heure par heure'!E55="","",'Heure par heure'!E55-N('Heure par heure'!E54))</f>
+        <v/>
+      </c>
+      <c r="E55" s="3">
+        <f>SUM(B55:D55)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$55</f>
+              <f>'Heure par heure'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$55</f>
+              <f>'Heure par heure'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$55</f>
+              <f>'Heure par heure'!$E$2:$E$56</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$55</f>
+              <f>'Heure par heure'!$B$2:$B$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$55</f>
+              <f>'Heure par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$55</f>
+              <f>'Heure par heure'!$F$2:$F$56</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$55</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$55</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$56</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$55</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$55</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>57</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4425,6 +4425,29 @@
         <v/>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:00</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F56" s="3">
+        <f>SUM(C56:E56)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4437,7 +4460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5650,6 +5673,28 @@
       </c>
       <c r="E55" s="3">
         <f>SUM(B55:D55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <f>'Heure par heure'!A56</f>
+        <v/>
+      </c>
+      <c r="B56" s="3">
+        <f>IF('Heure par heure'!C56="","",'Heure par heure'!C56-N('Heure par heure'!C55))</f>
+        <v/>
+      </c>
+      <c r="C56" s="3">
+        <f>IF('Heure par heure'!D56="","",'Heure par heure'!D56-N('Heure par heure'!D55))</f>
+        <v/>
+      </c>
+      <c r="D56" s="3">
+        <f>IF('Heure par heure'!E56="","",'Heure par heure'!E56-N('Heure par heure'!E55))</f>
+        <v/>
+      </c>
+      <c r="E56" s="3">
+        <f>SUM(B56:D56)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$56</f>
+              <f>'Heure par heure'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$56</f>
+              <f>'Heure par heure'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$56</f>
+              <f>'Heure par heure'!$E$2:$E$57</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$56</f>
+              <f>'Heure par heure'!$B$2:$B$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$56</f>
+              <f>'Heure par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$56</f>
+              <f>'Heure par heure'!$F$2:$F$57</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$56</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$56</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$57</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$56</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$56</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4448,6 +4448,29 @@
         <v/>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 18:00</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F57" s="3">
+        <f>SUM(C57:E57)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4460,7 +4483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5695,6 +5718,28 @@
       </c>
       <c r="E56" s="3">
         <f>SUM(B56:D56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <f>'Heure par heure'!A57</f>
+        <v/>
+      </c>
+      <c r="B57" s="3">
+        <f>IF('Heure par heure'!C57="","",'Heure par heure'!C57-N('Heure par heure'!C56))</f>
+        <v/>
+      </c>
+      <c r="C57" s="3">
+        <f>IF('Heure par heure'!D57="","",'Heure par heure'!D57-N('Heure par heure'!D56))</f>
+        <v/>
+      </c>
+      <c r="D57" s="3">
+        <f>IF('Heure par heure'!E57="","",'Heure par heure'!E57-N('Heure par heure'!E56))</f>
+        <v/>
+      </c>
+      <c r="E57" s="3">
+        <f>SUM(B57:D57)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$57</f>
+              <f>'Heure par heure'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$57</f>
+              <f>'Heure par heure'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$57</f>
+              <f>'Heure par heure'!$E$2:$E$58</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$57</f>
+              <f>'Heure par heure'!$B$2:$B$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$57</f>
+              <f>'Heure par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$57</f>
+              <f>'Heure par heure'!$F$2:$F$58</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$57</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$57</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$58</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$57</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$57</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4471,6 +4471,29 @@
         <v/>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 19:00</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F58" s="3">
+        <f>SUM(C58:E58)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4483,7 +4506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5740,6 +5763,28 @@
       </c>
       <c r="E57" s="3">
         <f>SUM(B57:D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <f>'Heure par heure'!A58</f>
+        <v/>
+      </c>
+      <c r="B58" s="3">
+        <f>IF('Heure par heure'!C58="","",'Heure par heure'!C58-N('Heure par heure'!C57))</f>
+        <v/>
+      </c>
+      <c r="C58" s="3">
+        <f>IF('Heure par heure'!D58="","",'Heure par heure'!D58-N('Heure par heure'!D57))</f>
+        <v/>
+      </c>
+      <c r="D58" s="3">
+        <f>IF('Heure par heure'!E58="","",'Heure par heure'!E58-N('Heure par heure'!E57))</f>
+        <v/>
+      </c>
+      <c r="E58" s="3">
+        <f>SUM(B58:D58)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$58</f>
+              <f>'Heure par heure'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$58</f>
+              <f>'Heure par heure'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$58</f>
+              <f>'Heure par heure'!$E$2:$E$59</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$58</f>
+              <f>'Heure par heure'!$B$2:$B$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$58</f>
+              <f>'Heure par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$58</f>
+              <f>'Heure par heure'!$F$2:$F$59</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$58</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$58</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$59</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$58</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$58</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4494,6 +4494,29 @@
         <v/>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 20:00</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F59" s="3">
+        <f>SUM(C59:E59)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4506,7 +4529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5785,6 +5808,28 @@
       </c>
       <c r="E58" s="3">
         <f>SUM(B58:D58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <f>'Heure par heure'!A59</f>
+        <v/>
+      </c>
+      <c r="B59" s="3">
+        <f>IF('Heure par heure'!C59="","",'Heure par heure'!C59-N('Heure par heure'!C58))</f>
+        <v/>
+      </c>
+      <c r="C59" s="3">
+        <f>IF('Heure par heure'!D59="","",'Heure par heure'!D59-N('Heure par heure'!D58))</f>
+        <v/>
+      </c>
+      <c r="D59" s="3">
+        <f>IF('Heure par heure'!E59="","",'Heure par heure'!E59-N('Heure par heure'!E58))</f>
+        <v/>
+      </c>
+      <c r="E59" s="3">
+        <f>SUM(B59:D59)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$59</f>
+              <f>'Heure par heure'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$59</f>
+              <f>'Heure par heure'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$59</f>
+              <f>'Heure par heure'!$E$2:$E$60</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$59</f>
+              <f>'Heure par heure'!$B$2:$B$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$59</f>
+              <f>'Heure par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$59</f>
+              <f>'Heure par heure'!$F$2:$F$60</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$59</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$59</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$60</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$59</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$59</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4517,6 +4517,29 @@
         <v/>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 21:00</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F60" s="3">
+        <f>SUM(C60:E60)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4529,7 +4552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5830,6 +5853,28 @@
       </c>
       <c r="E59" s="3">
         <f>SUM(B59:D59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <f>'Heure par heure'!A60</f>
+        <v/>
+      </c>
+      <c r="B60" s="3">
+        <f>IF('Heure par heure'!C60="","",'Heure par heure'!C60-N('Heure par heure'!C59))</f>
+        <v/>
+      </c>
+      <c r="C60" s="3">
+        <f>IF('Heure par heure'!D60="","",'Heure par heure'!D60-N('Heure par heure'!D59))</f>
+        <v/>
+      </c>
+      <c r="D60" s="3">
+        <f>IF('Heure par heure'!E60="","",'Heure par heure'!E60-N('Heure par heure'!E59))</f>
+        <v/>
+      </c>
+      <c r="E60" s="3">
+        <f>SUM(B60:D60)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$60</f>
+              <f>'Heure par heure'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$60</f>
+              <f>'Heure par heure'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$60</f>
+              <f>'Heure par heure'!$E$2:$E$61</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$60</f>
+              <f>'Heure par heure'!$B$2:$B$61</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$60</f>
+              <f>'Heure par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$60</f>
+              <f>'Heure par heure'!$F$2:$F$61</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$60</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$60</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$61</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$60</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$60</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4540,6 +4540,29 @@
         <v/>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28 22:00</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F61" s="3">
+        <f>SUM(C61:E61)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4552,7 +4575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5875,6 +5898,28 @@
       </c>
       <c r="E60" s="3">
         <f>SUM(B60:D60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <f>'Heure par heure'!A61</f>
+        <v/>
+      </c>
+      <c r="B61" s="3">
+        <f>IF('Heure par heure'!C61="","",'Heure par heure'!C61-N('Heure par heure'!C60))</f>
+        <v/>
+      </c>
+      <c r="C61" s="3">
+        <f>IF('Heure par heure'!D61="","",'Heure par heure'!D61-N('Heure par heure'!D60))</f>
+        <v/>
+      </c>
+      <c r="D61" s="3">
+        <f>IF('Heure par heure'!E61="","",'Heure par heure'!E61-N('Heure par heure'!E60))</f>
+        <v/>
+      </c>
+      <c r="E61" s="3">
+        <f>SUM(B61:D61)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$61</f>
+              <f>'Heure par heure'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$61</f>
+              <f>'Heure par heure'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$61</f>
+              <f>'Heure par heure'!$E$2:$E$62</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$61</f>
+              <f>'Heure par heure'!$B$2:$B$62</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$61</f>
+              <f>'Heure par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$61</f>
+              <f>'Heure par heure'!$F$2:$F$62</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$61</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$61</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$62</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$61</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$61</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4563,6 +4563,29 @@
         <v/>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 06:00</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F62" s="3">
+        <f>SUM(C62:E62)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4575,7 +4598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5920,6 +5943,28 @@
       </c>
       <c r="E61" s="3">
         <f>SUM(B61:D61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <f>'Heure par heure'!A62</f>
+        <v/>
+      </c>
+      <c r="B62" s="3">
+        <f>IF('Heure par heure'!C62="","",'Heure par heure'!C62-N('Heure par heure'!C61))</f>
+        <v/>
+      </c>
+      <c r="C62" s="3">
+        <f>IF('Heure par heure'!D62="","",'Heure par heure'!D62-N('Heure par heure'!D61))</f>
+        <v/>
+      </c>
+      <c r="D62" s="3">
+        <f>IF('Heure par heure'!E62="","",'Heure par heure'!E62-N('Heure par heure'!E61))</f>
+        <v/>
+      </c>
+      <c r="E62" s="3">
+        <f>SUM(B62:D62)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$62</f>
+              <f>'Heure par heure'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$62</f>
+              <f>'Heure par heure'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$62</f>
+              <f>'Heure par heure'!$E$2:$E$63</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$62</f>
+              <f>'Heure par heure'!$B$2:$B$63</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$62</f>
+              <f>'Heure par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$62</f>
+              <f>'Heure par heure'!$F$2:$F$63</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$62</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$62</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$63</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$62</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$62</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>65</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4586,6 +4586,29 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 07:00</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F63" s="3">
+        <f>SUM(C63:E63)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4598,7 +4621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5965,6 +5988,28 @@
       </c>
       <c r="E62" s="3">
         <f>SUM(B62:D62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <f>'Heure par heure'!A63</f>
+        <v/>
+      </c>
+      <c r="B63" s="3">
+        <f>IF('Heure par heure'!C63="","",'Heure par heure'!C63-N('Heure par heure'!C62))</f>
+        <v/>
+      </c>
+      <c r="C63" s="3">
+        <f>IF('Heure par heure'!D63="","",'Heure par heure'!D63-N('Heure par heure'!D62))</f>
+        <v/>
+      </c>
+      <c r="D63" s="3">
+        <f>IF('Heure par heure'!E63="","",'Heure par heure'!E63-N('Heure par heure'!E62))</f>
+        <v/>
+      </c>
+      <c r="E63" s="3">
+        <f>SUM(B63:D63)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$63</f>
+              <f>'Heure par heure'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$63</f>
+              <f>'Heure par heure'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$63</f>
+              <f>'Heure par heure'!$E$2:$E$64</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$63</f>
+              <f>'Heure par heure'!$B$2:$B$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$63</f>
+              <f>'Heure par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$63</f>
+              <f>'Heure par heure'!$F$2:$F$64</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$63</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$63</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$64</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$63</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$63</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3362,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4609,6 +4609,29 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 08:00</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F64" s="3">
+        <f>SUM(C64:E64)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4621,7 +4644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6010,6 +6033,28 @@
       </c>
       <c r="E63" s="3">
         <f>SUM(B63:D63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <f>'Heure par heure'!A64</f>
+        <v/>
+      </c>
+      <c r="B64" s="3">
+        <f>IF('Heure par heure'!C64="","",'Heure par heure'!C64-N('Heure par heure'!C63))</f>
+        <v/>
+      </c>
+      <c r="C64" s="3">
+        <f>IF('Heure par heure'!D64="","",'Heure par heure'!D64-N('Heure par heure'!D63))</f>
+        <v/>
+      </c>
+      <c r="D64" s="3">
+        <f>IF('Heure par heure'!E64="","",'Heure par heure'!E64-N('Heure par heure'!E63))</f>
+        <v/>
+      </c>
+      <c r="E64" s="3">
+        <f>SUM(B64:D64)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$5</f>
+              <f>'Jour par jour'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -954,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$5</f>
+              <f>'Jour par jour'!$E$2:$E$6</f>
             </numRef>
           </val>
         </ser>
@@ -981,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$5</f>
+              <f>'Jour par jour'!$L$2:$L$6</f>
             </numRef>
           </val>
         </ser>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$5</f>
+              <f>'Jour par jour'!$F$2:$F$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$5</f>
+              <f>'Jour par jour'!$H$2:$H$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1236,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$5</f>
+              <f>'Jour par jour'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$5</f>
+              <f>'Jour par jour'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1729,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$5</f>
+              <f>'Évolution par vidéo'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1761,12 +1761,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$5</f>
+              <f>'Évolution par vidéo'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$5</f>
+              <f>'Évolution par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$5</f>
+              <f>'Évolution par vidéo'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -1891,12 +1891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$5</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$6</f>
             </numRef>
           </val>
         </ser>
@@ -1915,12 +1915,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$5</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$6</f>
             </numRef>
           </val>
         </ser>
@@ -1939,12 +1939,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$5</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$5</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$6</f>
             </numRef>
           </val>
         </ser>
@@ -2157,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2184,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2619,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2882,6 +2882,51 @@
       </c>
       <c r="M5" s="3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <f>IF(ROW()=2,"",B6-B5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>337</v>
+      </c>
+      <c r="E6" s="3">
+        <f>IF(ROW()=2,D6,D6-D5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3130,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3206,6 +3251,22 @@
         <v>101</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3221,7 +3282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3347,6 +3408,29 @@
       </c>
       <c r="E5" s="3">
         <f>SUM(B5:D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>IF('Évolution par vidéo'!B6="","",'Évolution par vidéo'!B6-N('Évolution par vidéo'!B5))</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>IF('Évolution par vidéo'!C6="","",'Évolution par vidéo'!C6-N('Évolution par vidéo'!C5))</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>IF('Évolution par vidéo'!D6="","",'Évolution par vidéo'!D6-N('Évolution par vidéo'!D5))</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM(B6:D6)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$64</f>
+              <f>'Heure par heure'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$64</f>
+              <f>'Heure par heure'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$64</f>
+              <f>'Heure par heure'!$E$2:$E$65</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$64</f>
+              <f>'Heure par heure'!$B$2:$B$65</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$64</f>
+              <f>'Heure par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$64</f>
+              <f>'Heure par heure'!$F$2:$F$65</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$64</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$64</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$65</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$64</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$64</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4716,6 +4716,29 @@
         <v/>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:00</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F65" s="3">
+        <f>SUM(C65:E65)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4728,7 +4751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6139,6 +6162,28 @@
       </c>
       <c r="E64" s="3">
         <f>SUM(B64:D64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <f>'Heure par heure'!A65</f>
+        <v/>
+      </c>
+      <c r="B65" s="3">
+        <f>IF('Heure par heure'!C65="","",'Heure par heure'!C65-N('Heure par heure'!C64))</f>
+        <v/>
+      </c>
+      <c r="C65" s="3">
+        <f>IF('Heure par heure'!D65="","",'Heure par heure'!D65-N('Heure par heure'!D64))</f>
+        <v/>
+      </c>
+      <c r="D65" s="3">
+        <f>IF('Heure par heure'!E65="","",'Heure par heure'!E65-N('Heure par heure'!E64))</f>
+        <v/>
+      </c>
+      <c r="E65" s="3">
+        <f>SUM(B65:D65)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$65</f>
+              <f>'Heure par heure'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$65</f>
+              <f>'Heure par heure'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$65</f>
+              <f>'Heure par heure'!$E$2:$E$66</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$65</f>
+              <f>'Heure par heure'!$B$2:$B$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$65</f>
+              <f>'Heure par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$65</f>
+              <f>'Heure par heure'!$F$2:$F$66</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$65</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$65</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$66</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$65</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$65</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4739,6 +4739,29 @@
         <v/>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 10:00</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F66" s="3">
+        <f>SUM(C66:E66)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4751,7 +4774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6184,6 +6207,28 @@
       </c>
       <c r="E65" s="3">
         <f>SUM(B65:D65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <f>'Heure par heure'!A66</f>
+        <v/>
+      </c>
+      <c r="B66" s="3">
+        <f>IF('Heure par heure'!C66="","",'Heure par heure'!C66-N('Heure par heure'!C65))</f>
+        <v/>
+      </c>
+      <c r="C66" s="3">
+        <f>IF('Heure par heure'!D66="","",'Heure par heure'!D66-N('Heure par heure'!D65))</f>
+        <v/>
+      </c>
+      <c r="D66" s="3">
+        <f>IF('Heure par heure'!E66="","",'Heure par heure'!E66-N('Heure par heure'!E65))</f>
+        <v/>
+      </c>
+      <c r="E66" s="3">
+        <f>SUM(B66:D66)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$66</f>
+              <f>'Heure par heure'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$66</f>
+              <f>'Heure par heure'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$66</f>
+              <f>'Heure par heure'!$E$2:$E$67</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$66</f>
+              <f>'Heure par heure'!$B$2:$B$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$66</f>
+              <f>'Heure par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$66</f>
+              <f>'Heure par heure'!$F$2:$F$67</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$66</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$66</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$67</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$66</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$66</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4762,6 +4762,29 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F67" s="3">
+        <f>SUM(C67:E67)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4774,7 +4797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6229,6 +6252,28 @@
       </c>
       <c r="E66" s="3">
         <f>SUM(B66:D66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <f>'Heure par heure'!A67</f>
+        <v/>
+      </c>
+      <c r="B67" s="3">
+        <f>IF('Heure par heure'!C67="","",'Heure par heure'!C67-N('Heure par heure'!C66))</f>
+        <v/>
+      </c>
+      <c r="C67" s="3">
+        <f>IF('Heure par heure'!D67="","",'Heure par heure'!D67-N('Heure par heure'!D66))</f>
+        <v/>
+      </c>
+      <c r="D67" s="3">
+        <f>IF('Heure par heure'!E67="","",'Heure par heure'!E67-N('Heure par heure'!E66))</f>
+        <v/>
+      </c>
+      <c r="E67" s="3">
+        <f>SUM(B67:D67)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$67</f>
+              <f>'Heure par heure'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$67</f>
+              <f>'Heure par heure'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$67</f>
+              <f>'Heure par heure'!$E$2:$E$68</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$67</f>
+              <f>'Heure par heure'!$B$2:$B$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$67</f>
+              <f>'Heure par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$67</f>
+              <f>'Heure par heure'!$F$2:$F$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$67</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$67</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$68</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$67</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$67</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>70</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4785,6 +4785,29 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:00</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F68" s="3">
+        <f>SUM(C68:E68)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4797,7 +4820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6274,6 +6297,28 @@
       </c>
       <c r="E67" s="3">
         <f>SUM(B67:D67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <f>'Heure par heure'!A68</f>
+        <v/>
+      </c>
+      <c r="B68" s="3">
+        <f>IF('Heure par heure'!C68="","",'Heure par heure'!C68-N('Heure par heure'!C67))</f>
+        <v/>
+      </c>
+      <c r="C68" s="3">
+        <f>IF('Heure par heure'!D68="","",'Heure par heure'!D68-N('Heure par heure'!D67))</f>
+        <v/>
+      </c>
+      <c r="D68" s="3">
+        <f>IF('Heure par heure'!E68="","",'Heure par heure'!E68-N('Heure par heure'!E67))</f>
+        <v/>
+      </c>
+      <c r="E68" s="3">
+        <f>SUM(B68:D68)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$68</f>
+              <f>'Heure par heure'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$68</f>
+              <f>'Heure par heure'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$68</f>
+              <f>'Heure par heure'!$E$2:$E$69</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$68</f>
+              <f>'Heure par heure'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$68</f>
+              <f>'Heure par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$68</f>
+              <f>'Heure par heure'!$F$2:$F$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$68</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$68</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$68</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$68</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4808,6 +4808,29 @@
         <v/>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F69" s="3">
+        <f>SUM(C69:E69)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4820,7 +4843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6319,6 +6342,28 @@
       </c>
       <c r="E68" s="3">
         <f>SUM(B68:D68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <f>'Heure par heure'!A69</f>
+        <v/>
+      </c>
+      <c r="B69" s="3">
+        <f>IF('Heure par heure'!C69="","",'Heure par heure'!C69-N('Heure par heure'!C68))</f>
+        <v/>
+      </c>
+      <c r="C69" s="3">
+        <f>IF('Heure par heure'!D69="","",'Heure par heure'!D69-N('Heure par heure'!D68))</f>
+        <v/>
+      </c>
+      <c r="D69" s="3">
+        <f>IF('Heure par heure'!E69="","",'Heure par heure'!E69-N('Heure par heure'!E68))</f>
+        <v/>
+      </c>
+      <c r="E69" s="3">
+        <f>SUM(B69:D69)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$69</f>
+              <f>'Heure par heure'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$69</f>
+              <f>'Heure par heure'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$69</f>
+              <f>'Heure par heure'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$69</f>
+              <f>'Heure par heure'!$B$2:$B$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$69</f>
+              <f>'Heure par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$69</f>
+              <f>'Heure par heure'!$F$2:$F$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$69</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$69</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$69</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$69</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>72</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4831,6 +4831,29 @@
         <v/>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:00</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F70" s="3">
+        <f>SUM(C70:E70)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4843,7 +4866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6364,6 +6387,28 @@
       </c>
       <c r="E69" s="3">
         <f>SUM(B69:D69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <f>'Heure par heure'!A70</f>
+        <v/>
+      </c>
+      <c r="B70" s="3">
+        <f>IF('Heure par heure'!C70="","",'Heure par heure'!C70-N('Heure par heure'!C69))</f>
+        <v/>
+      </c>
+      <c r="C70" s="3">
+        <f>IF('Heure par heure'!D70="","",'Heure par heure'!D70-N('Heure par heure'!D69))</f>
+        <v/>
+      </c>
+      <c r="D70" s="3">
+        <f>IF('Heure par heure'!E70="","",'Heure par heure'!E70-N('Heure par heure'!E69))</f>
+        <v/>
+      </c>
+      <c r="E70" s="3">
+        <f>SUM(B70:D70)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$70</f>
+              <f>'Heure par heure'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$70</f>
+              <f>'Heure par heure'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$70</f>
+              <f>'Heure par heure'!$E$2:$E$71</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$70</f>
+              <f>'Heure par heure'!$B$2:$B$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$70</f>
+              <f>'Heure par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$70</f>
+              <f>'Heure par heure'!$F$2:$F$71</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$70</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$70</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$71</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$70</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$70</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4854,6 +4854,29 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 15:00</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F71" s="3">
+        <f>SUM(C71:E71)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4866,7 +4889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6409,6 +6432,28 @@
       </c>
       <c r="E70" s="3">
         <f>SUM(B70:D70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <f>'Heure par heure'!A71</f>
+        <v/>
+      </c>
+      <c r="B71" s="3">
+        <f>IF('Heure par heure'!C71="","",'Heure par heure'!C71-N('Heure par heure'!C70))</f>
+        <v/>
+      </c>
+      <c r="C71" s="3">
+        <f>IF('Heure par heure'!D71="","",'Heure par heure'!D71-N('Heure par heure'!D70))</f>
+        <v/>
+      </c>
+      <c r="D71" s="3">
+        <f>IF('Heure par heure'!E71="","",'Heure par heure'!E71-N('Heure par heure'!E70))</f>
+        <v/>
+      </c>
+      <c r="E71" s="3">
+        <f>SUM(B71:D71)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$71</f>
+              <f>'Heure par heure'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$71</f>
+              <f>'Heure par heure'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$71</f>
+              <f>'Heure par heure'!$E$2:$E$72</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$71</f>
+              <f>'Heure par heure'!$B$2:$B$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$71</f>
+              <f>'Heure par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$71</f>
+              <f>'Heure par heure'!$F$2:$F$72</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$71</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$71</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$72</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$71</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$71</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>73</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4877,6 +4877,29 @@
         <v/>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 16:00</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F72" s="3">
+        <f>SUM(C72:E72)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4889,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6454,6 +6477,28 @@
       </c>
       <c r="E71" s="3">
         <f>SUM(B71:D71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <f>'Heure par heure'!A72</f>
+        <v/>
+      </c>
+      <c r="B72" s="3">
+        <f>IF('Heure par heure'!C72="","",'Heure par heure'!C72-N('Heure par heure'!C71))</f>
+        <v/>
+      </c>
+      <c r="C72" s="3">
+        <f>IF('Heure par heure'!D72="","",'Heure par heure'!D72-N('Heure par heure'!D71))</f>
+        <v/>
+      </c>
+      <c r="D72" s="3">
+        <f>IF('Heure par heure'!E72="","",'Heure par heure'!E72-N('Heure par heure'!E71))</f>
+        <v/>
+      </c>
+      <c r="E72" s="3">
+        <f>SUM(B72:D72)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$72</f>
+              <f>'Heure par heure'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$72</f>
+              <f>'Heure par heure'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$72</f>
+              <f>'Heure par heure'!$E$2:$E$73</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$72</f>
+              <f>'Heure par heure'!$B$2:$B$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$72</f>
+              <f>'Heure par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$72</f>
+              <f>'Heure par heure'!$F$2:$F$73</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$72</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$72</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$73</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$72</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$72</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4900,6 +4900,29 @@
         <v/>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:00</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F73" s="3">
+        <f>SUM(C73:E73)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4912,7 +4935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6499,6 +6522,28 @@
       </c>
       <c r="E72" s="3">
         <f>SUM(B72:D72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <f>'Heure par heure'!A73</f>
+        <v/>
+      </c>
+      <c r="B73" s="3">
+        <f>IF('Heure par heure'!C73="","",'Heure par heure'!C73-N('Heure par heure'!C72))</f>
+        <v/>
+      </c>
+      <c r="C73" s="3">
+        <f>IF('Heure par heure'!D73="","",'Heure par heure'!D73-N('Heure par heure'!D72))</f>
+        <v/>
+      </c>
+      <c r="D73" s="3">
+        <f>IF('Heure par heure'!E73="","",'Heure par heure'!E73-N('Heure par heure'!E72))</f>
+        <v/>
+      </c>
+      <c r="E73" s="3">
+        <f>SUM(B73:D73)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$73</f>
+              <f>'Heure par heure'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$73</f>
+              <f>'Heure par heure'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$73</f>
+              <f>'Heure par heure'!$E$2:$E$74</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$73</f>
+              <f>'Heure par heure'!$B$2:$B$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$73</f>
+              <f>'Heure par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$73</f>
+              <f>'Heure par heure'!$F$2:$F$74</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$73</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$73</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$74</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$73</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$73</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4923,6 +4923,29 @@
         <v/>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:00</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F74" s="3">
+        <f>SUM(C74:E74)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4935,7 +4958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6544,6 +6567,28 @@
       </c>
       <c r="E73" s="3">
         <f>SUM(B73:D73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <f>'Heure par heure'!A74</f>
+        <v/>
+      </c>
+      <c r="B74" s="3">
+        <f>IF('Heure par heure'!C74="","",'Heure par heure'!C74-N('Heure par heure'!C73))</f>
+        <v/>
+      </c>
+      <c r="C74" s="3">
+        <f>IF('Heure par heure'!D74="","",'Heure par heure'!D74-N('Heure par heure'!D73))</f>
+        <v/>
+      </c>
+      <c r="D74" s="3">
+        <f>IF('Heure par heure'!E74="","",'Heure par heure'!E74-N('Heure par heure'!E73))</f>
+        <v/>
+      </c>
+      <c r="E74" s="3">
+        <f>SUM(B74:D74)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$74</f>
+              <f>'Heure par heure'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$74</f>
+              <f>'Heure par heure'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$74</f>
+              <f>'Heure par heure'!$E$2:$E$75</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$74</f>
+              <f>'Heure par heure'!$B$2:$B$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$74</f>
+              <f>'Heure par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$74</f>
+              <f>'Heure par heure'!$F$2:$F$75</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$74</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$74</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$75</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$74</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$74</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4946,6 +4946,29 @@
         <v/>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:00</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F75" s="3">
+        <f>SUM(C75:E75)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4958,7 +4981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6589,6 +6612,28 @@
       </c>
       <c r="E74" s="3">
         <f>SUM(B74:D74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <f>'Heure par heure'!A75</f>
+        <v/>
+      </c>
+      <c r="B75" s="3">
+        <f>IF('Heure par heure'!C75="","",'Heure par heure'!C75-N('Heure par heure'!C74))</f>
+        <v/>
+      </c>
+      <c r="C75" s="3">
+        <f>IF('Heure par heure'!D75="","",'Heure par heure'!D75-N('Heure par heure'!D74))</f>
+        <v/>
+      </c>
+      <c r="D75" s="3">
+        <f>IF('Heure par heure'!E75="","",'Heure par heure'!E75-N('Heure par heure'!E74))</f>
+        <v/>
+      </c>
+      <c r="E75" s="3">
+        <f>SUM(B75:D75)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$75</f>
+              <f>'Heure par heure'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$75</f>
+              <f>'Heure par heure'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$75</f>
+              <f>'Heure par heure'!$E$2:$E$76</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$75</f>
+              <f>'Heure par heure'!$B$2:$B$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$75</f>
+              <f>'Heure par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$75</f>
+              <f>'Heure par heure'!$F$2:$F$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$75</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$75</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$76</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$75</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$75</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4969,6 +4969,29 @@
         <v/>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:00</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F76" s="3">
+        <f>SUM(C76:E76)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4981,7 +5004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6634,6 +6657,28 @@
       </c>
       <c r="E75" s="3">
         <f>SUM(B75:D75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <f>'Heure par heure'!A76</f>
+        <v/>
+      </c>
+      <c r="B76" s="3">
+        <f>IF('Heure par heure'!C76="","",'Heure par heure'!C76-N('Heure par heure'!C75))</f>
+        <v/>
+      </c>
+      <c r="C76" s="3">
+        <f>IF('Heure par heure'!D76="","",'Heure par heure'!D76-N('Heure par heure'!D75))</f>
+        <v/>
+      </c>
+      <c r="D76" s="3">
+        <f>IF('Heure par heure'!E76="","",'Heure par heure'!E76-N('Heure par heure'!E75))</f>
+        <v/>
+      </c>
+      <c r="E76" s="3">
+        <f>SUM(B76:D76)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$76</f>
+              <f>'Heure par heure'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$76</f>
+              <f>'Heure par heure'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$76</f>
+              <f>'Heure par heure'!$E$2:$E$77</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$76</f>
+              <f>'Heure par heure'!$B$2:$B$77</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$76</f>
+              <f>'Heure par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$76</f>
+              <f>'Heure par heure'!$F$2:$F$77</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$76</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$76</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$77</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$76</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$76</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4992,6 +4992,29 @@
         <v/>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 21:00</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F77" s="3">
+        <f>SUM(C77:E77)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5004,7 +5027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6679,6 +6702,28 @@
       </c>
       <c r="E76" s="3">
         <f>SUM(B76:D76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <f>'Heure par heure'!A77</f>
+        <v/>
+      </c>
+      <c r="B77" s="3">
+        <f>IF('Heure par heure'!C77="","",'Heure par heure'!C77-N('Heure par heure'!C76))</f>
+        <v/>
+      </c>
+      <c r="C77" s="3">
+        <f>IF('Heure par heure'!D77="","",'Heure par heure'!D77-N('Heure par heure'!D76))</f>
+        <v/>
+      </c>
+      <c r="D77" s="3">
+        <f>IF('Heure par heure'!E77="","",'Heure par heure'!E77-N('Heure par heure'!E76))</f>
+        <v/>
+      </c>
+      <c r="E77" s="3">
+        <f>SUM(B77:D77)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$77</f>
+              <f>'Heure par heure'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$77</f>
+              <f>'Heure par heure'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$77</f>
+              <f>'Heure par heure'!$E$2:$E$78</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$77</f>
+              <f>'Heure par heure'!$B$2:$B$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$77</f>
+              <f>'Heure par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$77</f>
+              <f>'Heure par heure'!$F$2:$F$78</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$77</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$77</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$78</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$77</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$77</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5015,6 +5015,29 @@
         <v/>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29 22:00</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F78" s="3">
+        <f>SUM(C78:E78)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5027,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6724,6 +6747,28 @@
       </c>
       <c r="E77" s="3">
         <f>SUM(B77:D77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <f>'Heure par heure'!A78</f>
+        <v/>
+      </c>
+      <c r="B78" s="3">
+        <f>IF('Heure par heure'!C78="","",'Heure par heure'!C78-N('Heure par heure'!C77))</f>
+        <v/>
+      </c>
+      <c r="C78" s="3">
+        <f>IF('Heure par heure'!D78="","",'Heure par heure'!D78-N('Heure par heure'!D77))</f>
+        <v/>
+      </c>
+      <c r="D78" s="3">
+        <f>IF('Heure par heure'!E78="","",'Heure par heure'!E78-N('Heure par heure'!E77))</f>
+        <v/>
+      </c>
+      <c r="E78" s="3">
+        <f>SUM(B78:D78)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$78</f>
+              <f>'Heure par heure'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$78</f>
+              <f>'Heure par heure'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$78</f>
+              <f>'Heure par heure'!$E$2:$E$79</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$78</f>
+              <f>'Heure par heure'!$B$2:$B$79</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$78</f>
+              <f>'Heure par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$78</f>
+              <f>'Heure par heure'!$F$2:$F$79</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$78</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$78</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$79</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$78</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$78</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5038,6 +5038,29 @@
         <v/>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:00</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F79" s="3">
+        <f>SUM(C79:E79)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5050,7 +5073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6769,6 +6792,28 @@
       </c>
       <c r="E78" s="3">
         <f>SUM(B78:D78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <f>'Heure par heure'!A79</f>
+        <v/>
+      </c>
+      <c r="B79" s="3">
+        <f>IF('Heure par heure'!C79="","",'Heure par heure'!C79-N('Heure par heure'!C78))</f>
+        <v/>
+      </c>
+      <c r="C79" s="3">
+        <f>IF('Heure par heure'!D79="","",'Heure par heure'!D79-N('Heure par heure'!D78))</f>
+        <v/>
+      </c>
+      <c r="D79" s="3">
+        <f>IF('Heure par heure'!E79="","",'Heure par heure'!E79-N('Heure par heure'!E78))</f>
+        <v/>
+      </c>
+      <c r="E79" s="3">
+        <f>SUM(B79:D79)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$79</f>
+              <f>'Heure par heure'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$79</f>
+              <f>'Heure par heure'!$D$2:$D$80</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$79</f>
+              <f>'Heure par heure'!$E$2:$E$80</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$79</f>
+              <f>'Heure par heure'!$B$2:$B$80</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$79</f>
+              <f>'Heure par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$79</f>
+              <f>'Heure par heure'!$F$2:$F$80</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$79</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$80</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$79</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$80</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$79</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$79</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$80</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5061,6 +5061,29 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 07:00</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F80" s="3">
+        <f>SUM(C80:E80)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5073,7 +5096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6814,6 +6837,28 @@
       </c>
       <c r="E79" s="3">
         <f>SUM(B79:D79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <f>'Heure par heure'!A80</f>
+        <v/>
+      </c>
+      <c r="B80" s="3">
+        <f>IF('Heure par heure'!C80="","",'Heure par heure'!C80-N('Heure par heure'!C79))</f>
+        <v/>
+      </c>
+      <c r="C80" s="3">
+        <f>IF('Heure par heure'!D80="","",'Heure par heure'!D80-N('Heure par heure'!D79))</f>
+        <v/>
+      </c>
+      <c r="D80" s="3">
+        <f>IF('Heure par heure'!E80="","",'Heure par heure'!E80-N('Heure par heure'!E79))</f>
+        <v/>
+      </c>
+      <c r="E80" s="3">
+        <f>SUM(B80:D80)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$80</f>
+              <f>'Heure par heure'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$80</f>
+              <f>'Heure par heure'!$D$2:$D$81</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$80</f>
+              <f>'Heure par heure'!$E$2:$E$81</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$80</f>
+              <f>'Heure par heure'!$B$2:$B$81</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$80</f>
+              <f>'Heure par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$80</f>
+              <f>'Heure par heure'!$F$2:$F$81</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$80</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$81</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$80</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$81</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$80</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$80</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$81</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3446,7 +3446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5084,6 +5084,29 @@
         <v/>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:00</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F81" s="3">
+        <f>SUM(C81:E81)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5096,7 +5119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6859,6 +6882,28 @@
       </c>
       <c r="E80" s="3">
         <f>SUM(B80:D80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <f>'Heure par heure'!A81</f>
+        <v/>
+      </c>
+      <c r="B81" s="3">
+        <f>IF('Heure par heure'!C81="","",'Heure par heure'!C81-N('Heure par heure'!C80))</f>
+        <v/>
+      </c>
+      <c r="C81" s="3">
+        <f>IF('Heure par heure'!D81="","",'Heure par heure'!D81-N('Heure par heure'!D80))</f>
+        <v/>
+      </c>
+      <c r="D81" s="3">
+        <f>IF('Heure par heure'!E81="","",'Heure par heure'!E81-N('Heure par heure'!E80))</f>
+        <v/>
+      </c>
+      <c r="E81" s="3">
+        <f>SUM(B81:D81)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$6</f>
+              <f>'Jour par jour'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -954,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$6</f>
+              <f>'Jour par jour'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -981,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$6</f>
+              <f>'Jour par jour'!$L$2:$L$7</f>
             </numRef>
           </val>
         </ser>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$6</f>
+              <f>'Jour par jour'!$F$2:$F$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$6</f>
+              <f>'Jour par jour'!$H$2:$H$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1236,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$6</f>
+              <f>'Jour par jour'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$6</f>
+              <f>'Jour par jour'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1729,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$6</f>
+              <f>'Évolution par vidéo'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1761,12 +1761,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$6</f>
+              <f>'Évolution par vidéo'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$6</f>
+              <f>'Évolution par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$6</f>
+              <f>'Évolution par vidéo'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -1891,12 +1891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$6</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -1915,12 +1915,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$6</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -1939,12 +1939,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$6</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$6</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -2157,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2184,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2619,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2926,6 +2926,51 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <f>IF(ROW()=2,"",B7-B6)</f>
+        <v/>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>337</v>
+      </c>
+      <c r="E7" s="3">
+        <f>IF(ROW()=2,D7,D7-D6)</f>
+        <v/>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3175,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3267,6 +3312,22 @@
         <v>101</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3282,7 +3343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3431,6 +3492,29 @@
       </c>
       <c r="E6" s="3">
         <f>SUM(B6:D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>IF('Évolution par vidéo'!B7="","",'Évolution par vidéo'!B7-N('Évolution par vidéo'!B6))</f>
+        <v/>
+      </c>
+      <c r="C7" s="3">
+        <f>IF('Évolution par vidéo'!C7="","",'Évolution par vidéo'!C7-N('Évolution par vidéo'!C6))</f>
+        <v/>
+      </c>
+      <c r="D7" s="3">
+        <f>IF('Évolution par vidéo'!D7="","",'Évolution par vidéo'!D7-N('Évolution par vidéo'!D6))</f>
+        <v/>
+      </c>
+      <c r="E7" s="3">
+        <f>SUM(B7:D7)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$81</f>
+              <f>'Heure par heure'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$81</f>
+              <f>'Heure par heure'!$D$2:$D$82</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$81</f>
+              <f>'Heure par heure'!$E$2:$E$82</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$81</f>
+              <f>'Heure par heure'!$B$2:$B$82</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$81</f>
+              <f>'Heure par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$81</f>
+              <f>'Heure par heure'!$F$2:$F$82</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$81</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$82</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$81</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$82</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$81</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$81</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$82</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5191,6 +5191,29 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 09:00</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F82" s="3">
+        <f>SUM(C82:E82)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5203,7 +5226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6988,6 +7011,28 @@
       </c>
       <c r="E81" s="3">
         <f>SUM(B81:D81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <f>'Heure par heure'!A82</f>
+        <v/>
+      </c>
+      <c r="B82" s="3">
+        <f>IF('Heure par heure'!C82="","",'Heure par heure'!C82-N('Heure par heure'!C81))</f>
+        <v/>
+      </c>
+      <c r="C82" s="3">
+        <f>IF('Heure par heure'!D82="","",'Heure par heure'!D82-N('Heure par heure'!D81))</f>
+        <v/>
+      </c>
+      <c r="D82" s="3">
+        <f>IF('Heure par heure'!E82="","",'Heure par heure'!E82-N('Heure par heure'!E81))</f>
+        <v/>
+      </c>
+      <c r="E82" s="3">
+        <f>SUM(B82:D82)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$82</f>
+              <f>'Heure par heure'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$82</f>
+              <f>'Heure par heure'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$82</f>
+              <f>'Heure par heure'!$E$2:$E$83</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$82</f>
+              <f>'Heure par heure'!$B$2:$B$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$82</f>
+              <f>'Heure par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$82</f>
+              <f>'Heure par heure'!$F$2:$F$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$82</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$83</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$82</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$83</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$82</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$82</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$83</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5214,6 +5214,29 @@
         <v/>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 10:00</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F83" s="3">
+        <f>SUM(C83:E83)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5226,7 +5249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7033,6 +7056,28 @@
       </c>
       <c r="E82" s="3">
         <f>SUM(B82:D82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <f>'Heure par heure'!A83</f>
+        <v/>
+      </c>
+      <c r="B83" s="3">
+        <f>IF('Heure par heure'!C83="","",'Heure par heure'!C83-N('Heure par heure'!C82))</f>
+        <v/>
+      </c>
+      <c r="C83" s="3">
+        <f>IF('Heure par heure'!D83="","",'Heure par heure'!D83-N('Heure par heure'!D82))</f>
+        <v/>
+      </c>
+      <c r="D83" s="3">
+        <f>IF('Heure par heure'!E83="","",'Heure par heure'!E83-N('Heure par heure'!E82))</f>
+        <v/>
+      </c>
+      <c r="E83" s="3">
+        <f>SUM(B83:D83)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$83</f>
+              <f>'Heure par heure'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$83</f>
+              <f>'Heure par heure'!$D$2:$D$84</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$83</f>
+              <f>'Heure par heure'!$E$2:$E$84</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$83</f>
+              <f>'Heure par heure'!$B$2:$B$84</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$83</f>
+              <f>'Heure par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$83</f>
+              <f>'Heure par heure'!$F$2:$F$84</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$83</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$84</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$83</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$84</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$83</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$83</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$84</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5237,6 +5237,29 @@
         <v/>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F84" s="3">
+        <f>SUM(C84:E84)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5249,7 +5272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7078,6 +7101,28 @@
       </c>
       <c r="E83" s="3">
         <f>SUM(B83:D83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <f>'Heure par heure'!A84</f>
+        <v/>
+      </c>
+      <c r="B84" s="3">
+        <f>IF('Heure par heure'!C84="","",'Heure par heure'!C84-N('Heure par heure'!C83))</f>
+        <v/>
+      </c>
+      <c r="C84" s="3">
+        <f>IF('Heure par heure'!D84="","",'Heure par heure'!D84-N('Heure par heure'!D83))</f>
+        <v/>
+      </c>
+      <c r="D84" s="3">
+        <f>IF('Heure par heure'!E84="","",'Heure par heure'!E84-N('Heure par heure'!E83))</f>
+        <v/>
+      </c>
+      <c r="E84" s="3">
+        <f>SUM(B84:D84)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$84</f>
+              <f>'Heure par heure'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$84</f>
+              <f>'Heure par heure'!$D$2:$D$85</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$84</f>
+              <f>'Heure par heure'!$E$2:$E$85</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$84</f>
+              <f>'Heure par heure'!$B$2:$B$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$84</f>
+              <f>'Heure par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$84</f>
+              <f>'Heure par heure'!$F$2:$F$85</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$84</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$85</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$84</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$85</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$84</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$84</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$85</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5260,6 +5260,29 @@
         <v/>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 12:00</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F85" s="3">
+        <f>SUM(C85:E85)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5272,7 +5295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7123,6 +7146,28 @@
       </c>
       <c r="E84" s="3">
         <f>SUM(B84:D84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <f>'Heure par heure'!A85</f>
+        <v/>
+      </c>
+      <c r="B85" s="3">
+        <f>IF('Heure par heure'!C85="","",'Heure par heure'!C85-N('Heure par heure'!C84))</f>
+        <v/>
+      </c>
+      <c r="C85" s="3">
+        <f>IF('Heure par heure'!D85="","",'Heure par heure'!D85-N('Heure par heure'!D84))</f>
+        <v/>
+      </c>
+      <c r="D85" s="3">
+        <f>IF('Heure par heure'!E85="","",'Heure par heure'!E85-N('Heure par heure'!E84))</f>
+        <v/>
+      </c>
+      <c r="E85" s="3">
+        <f>SUM(B85:D85)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$85</f>
+              <f>'Heure par heure'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$85</f>
+              <f>'Heure par heure'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$85</f>
+              <f>'Heure par heure'!$E$2:$E$86</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$85</f>
+              <f>'Heure par heure'!$B$2:$B$86</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$85</f>
+              <f>'Heure par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$85</f>
+              <f>'Heure par heure'!$F$2:$F$86</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$85</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$86</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$85</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$86</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$85</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$85</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$86</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5283,6 +5283,29 @@
         <v/>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 13:00</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F86" s="3">
+        <f>SUM(C86:E86)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5295,7 +5318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7168,6 +7191,28 @@
       </c>
       <c r="E85" s="3">
         <f>SUM(B85:D85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <f>'Heure par heure'!A86</f>
+        <v/>
+      </c>
+      <c r="B86" s="3">
+        <f>IF('Heure par heure'!C86="","",'Heure par heure'!C86-N('Heure par heure'!C85))</f>
+        <v/>
+      </c>
+      <c r="C86" s="3">
+        <f>IF('Heure par heure'!D86="","",'Heure par heure'!D86-N('Heure par heure'!D85))</f>
+        <v/>
+      </c>
+      <c r="D86" s="3">
+        <f>IF('Heure par heure'!E86="","",'Heure par heure'!E86-N('Heure par heure'!E85))</f>
+        <v/>
+      </c>
+      <c r="E86" s="3">
+        <f>SUM(B86:D86)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$86</f>
+              <f>'Heure par heure'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$86</f>
+              <f>'Heure par heure'!$D$2:$D$87</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$86</f>
+              <f>'Heure par heure'!$E$2:$E$87</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$86</f>
+              <f>'Heure par heure'!$B$2:$B$87</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$86</f>
+              <f>'Heure par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$86</f>
+              <f>'Heure par heure'!$F$2:$F$87</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$86</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$87</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$86</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$87</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$86</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$86</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$87</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5306,6 +5306,29 @@
         <v/>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:00</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F87" s="3">
+        <f>SUM(C87:E87)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5318,7 +5341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7213,6 +7236,28 @@
       </c>
       <c r="E86" s="3">
         <f>SUM(B86:D86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <f>'Heure par heure'!A87</f>
+        <v/>
+      </c>
+      <c r="B87" s="3">
+        <f>IF('Heure par heure'!C87="","",'Heure par heure'!C87-N('Heure par heure'!C86))</f>
+        <v/>
+      </c>
+      <c r="C87" s="3">
+        <f>IF('Heure par heure'!D87="","",'Heure par heure'!D87-N('Heure par heure'!D86))</f>
+        <v/>
+      </c>
+      <c r="D87" s="3">
+        <f>IF('Heure par heure'!E87="","",'Heure par heure'!E87-N('Heure par heure'!E86))</f>
+        <v/>
+      </c>
+      <c r="E87" s="3">
+        <f>SUM(B87:D87)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$87</f>
+              <f>'Heure par heure'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$87</f>
+              <f>'Heure par heure'!$D$2:$D$88</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$87</f>
+              <f>'Heure par heure'!$E$2:$E$88</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$87</f>
+              <f>'Heure par heure'!$B$2:$B$88</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$87</f>
+              <f>'Heure par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$87</f>
+              <f>'Heure par heure'!$F$2:$F$88</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$87</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$88</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$87</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$88</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$87</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$87</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$88</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>106</row>
+      <row>107</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5329,6 +5329,29 @@
         <v/>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:00</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F88" s="3">
+        <f>SUM(C88:E88)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5341,7 +5364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7258,6 +7281,28 @@
       </c>
       <c r="E87" s="3">
         <f>SUM(B87:D87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <f>'Heure par heure'!A88</f>
+        <v/>
+      </c>
+      <c r="B88" s="3">
+        <f>IF('Heure par heure'!C88="","",'Heure par heure'!C88-N('Heure par heure'!C87))</f>
+        <v/>
+      </c>
+      <c r="C88" s="3">
+        <f>IF('Heure par heure'!D88="","",'Heure par heure'!D88-N('Heure par heure'!D87))</f>
+        <v/>
+      </c>
+      <c r="D88" s="3">
+        <f>IF('Heure par heure'!E88="","",'Heure par heure'!E88-N('Heure par heure'!E87))</f>
+        <v/>
+      </c>
+      <c r="E88" s="3">
+        <f>SUM(B88:D88)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$88</f>
+              <f>'Heure par heure'!$C$2:$C$89</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$88</f>
+              <f>'Heure par heure'!$D$2:$D$89</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$88</f>
+              <f>'Heure par heure'!$E$2:$E$89</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$88</f>
+              <f>'Heure par heure'!$B$2:$B$89</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$88</f>
+              <f>'Heure par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$88</f>
+              <f>'Heure par heure'!$F$2:$F$89</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$88</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$89</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$88</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$89</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$88</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$88</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$89</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>107</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5352,6 +5352,29 @@
         <v/>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 16:00</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F89" s="3">
+        <f>SUM(C89:E89)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5364,7 +5387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7303,6 +7326,28 @@
       </c>
       <c r="E88" s="3">
         <f>SUM(B88:D88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <f>'Heure par heure'!A89</f>
+        <v/>
+      </c>
+      <c r="B89" s="3">
+        <f>IF('Heure par heure'!C89="","",'Heure par heure'!C89-N('Heure par heure'!C88))</f>
+        <v/>
+      </c>
+      <c r="C89" s="3">
+        <f>IF('Heure par heure'!D89="","",'Heure par heure'!D89-N('Heure par heure'!D88))</f>
+        <v/>
+      </c>
+      <c r="D89" s="3">
+        <f>IF('Heure par heure'!E89="","",'Heure par heure'!E89-N('Heure par heure'!E88))</f>
+        <v/>
+      </c>
+      <c r="E89" s="3">
+        <f>SUM(B89:D89)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$89</f>
+              <f>'Heure par heure'!$C$2:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$89</f>
+              <f>'Heure par heure'!$D$2:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$89</f>
+              <f>'Heure par heure'!$E$2:$E$90</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$89</f>
+              <f>'Heure par heure'!$B$2:$B$90</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$89</f>
+              <f>'Heure par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$89</f>
+              <f>'Heure par heure'!$F$2:$F$90</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$89</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$89</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$90</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$89</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$89</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$90</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>108</row>
+      <row>109</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5375,6 +5375,29 @@
         <v/>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:00</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F90" s="3">
+        <f>SUM(C90:E90)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5387,7 +5410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7348,6 +7371,28 @@
       </c>
       <c r="E89" s="3">
         <f>SUM(B89:D89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <f>'Heure par heure'!A90</f>
+        <v/>
+      </c>
+      <c r="B90" s="3">
+        <f>IF('Heure par heure'!C90="","",'Heure par heure'!C90-N('Heure par heure'!C89))</f>
+        <v/>
+      </c>
+      <c r="C90" s="3">
+        <f>IF('Heure par heure'!D90="","",'Heure par heure'!D90-N('Heure par heure'!D89))</f>
+        <v/>
+      </c>
+      <c r="D90" s="3">
+        <f>IF('Heure par heure'!E90="","",'Heure par heure'!E90-N('Heure par heure'!E89))</f>
+        <v/>
+      </c>
+      <c r="E90" s="3">
+        <f>SUM(B90:D90)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$90</f>
+              <f>'Heure par heure'!$C$2:$C$91</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$90</f>
+              <f>'Heure par heure'!$D$2:$D$91</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$90</f>
+              <f>'Heure par heure'!$E$2:$E$91</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$90</f>
+              <f>'Heure par heure'!$B$2:$B$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$90</f>
+              <f>'Heure par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$90</f>
+              <f>'Heure par heure'!$F$2:$F$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$90</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$91</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$90</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$91</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$90</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$90</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$91</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>109</row>
+      <row>110</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5398,6 +5398,29 @@
         <v/>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 18:00</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F91" s="3">
+        <f>SUM(C91:E91)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5410,7 +5433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7393,6 +7416,28 @@
       </c>
       <c r="E90" s="3">
         <f>SUM(B90:D90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <f>'Heure par heure'!A91</f>
+        <v/>
+      </c>
+      <c r="B91" s="3">
+        <f>IF('Heure par heure'!C91="","",'Heure par heure'!C91-N('Heure par heure'!C90))</f>
+        <v/>
+      </c>
+      <c r="C91" s="3">
+        <f>IF('Heure par heure'!D91="","",'Heure par heure'!D91-N('Heure par heure'!D90))</f>
+        <v/>
+      </c>
+      <c r="D91" s="3">
+        <f>IF('Heure par heure'!E91="","",'Heure par heure'!E91-N('Heure par heure'!E90))</f>
+        <v/>
+      </c>
+      <c r="E91" s="3">
+        <f>SUM(B91:D91)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$91</f>
+              <f>'Heure par heure'!$C$2:$C$92</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$91</f>
+              <f>'Heure par heure'!$D$2:$D$92</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$91</f>
+              <f>'Heure par heure'!$E$2:$E$92</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$91</f>
+              <f>'Heure par heure'!$B$2:$B$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$91</f>
+              <f>'Heure par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$91</f>
+              <f>'Heure par heure'!$F$2:$F$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$91</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$92</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$91</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$92</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$91</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$91</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$92</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>110</row>
+      <row>111</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5421,6 +5421,29 @@
         <v/>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 19:00</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F92" s="3">
+        <f>SUM(C92:E92)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5433,7 +5456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7438,6 +7461,28 @@
       </c>
       <c r="E91" s="3">
         <f>SUM(B91:D91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <f>'Heure par heure'!A92</f>
+        <v/>
+      </c>
+      <c r="B92" s="3">
+        <f>IF('Heure par heure'!C92="","",'Heure par heure'!C92-N('Heure par heure'!C91))</f>
+        <v/>
+      </c>
+      <c r="C92" s="3">
+        <f>IF('Heure par heure'!D92="","",'Heure par heure'!D92-N('Heure par heure'!D91))</f>
+        <v/>
+      </c>
+      <c r="D92" s="3">
+        <f>IF('Heure par heure'!E92="","",'Heure par heure'!E92-N('Heure par heure'!E91))</f>
+        <v/>
+      </c>
+      <c r="E92" s="3">
+        <f>SUM(B92:D92)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$92</f>
+              <f>'Heure par heure'!$C$2:$C$93</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$92</f>
+              <f>'Heure par heure'!$D$2:$D$93</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$92</f>
+              <f>'Heure par heure'!$E$2:$E$93</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$92</f>
+              <f>'Heure par heure'!$B$2:$B$93</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$92</f>
+              <f>'Heure par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$92</f>
+              <f>'Heure par heure'!$F$2:$F$93</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$92</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$93</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$92</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$93</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$92</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$92</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$93</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>111</row>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5444,6 +5444,29 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 20:00</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F93" s="3">
+        <f>SUM(C93:E93)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5456,7 +5479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7483,6 +7506,28 @@
       </c>
       <c r="E92" s="3">
         <f>SUM(B92:D92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <f>'Heure par heure'!A93</f>
+        <v/>
+      </c>
+      <c r="B93" s="3">
+        <f>IF('Heure par heure'!C93="","",'Heure par heure'!C93-N('Heure par heure'!C92))</f>
+        <v/>
+      </c>
+      <c r="C93" s="3">
+        <f>IF('Heure par heure'!D93="","",'Heure par heure'!D93-N('Heure par heure'!D92))</f>
+        <v/>
+      </c>
+      <c r="D93" s="3">
+        <f>IF('Heure par heure'!E93="","",'Heure par heure'!E93-N('Heure par heure'!E92))</f>
+        <v/>
+      </c>
+      <c r="E93" s="3">
+        <f>SUM(B93:D93)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$93</f>
+              <f>'Heure par heure'!$C$2:$C$94</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$93</f>
+              <f>'Heure par heure'!$D$2:$D$94</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$93</f>
+              <f>'Heure par heure'!$E$2:$E$94</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$93</f>
+              <f>'Heure par heure'!$B$2:$B$94</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$93</f>
+              <f>'Heure par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$93</f>
+              <f>'Heure par heure'!$F$2:$F$94</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$93</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$94</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$93</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$94</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$93</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$93</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$94</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5467,6 +5467,29 @@
         <v/>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F94" s="3">
+        <f>SUM(C94:E94)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5479,7 +5502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7528,6 +7551,28 @@
       </c>
       <c r="E93" s="3">
         <f>SUM(B93:D93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <f>'Heure par heure'!A94</f>
+        <v/>
+      </c>
+      <c r="B94" s="3">
+        <f>IF('Heure par heure'!C94="","",'Heure par heure'!C94-N('Heure par heure'!C93))</f>
+        <v/>
+      </c>
+      <c r="C94" s="3">
+        <f>IF('Heure par heure'!D94="","",'Heure par heure'!D94-N('Heure par heure'!D93))</f>
+        <v/>
+      </c>
+      <c r="D94" s="3">
+        <f>IF('Heure par heure'!E94="","",'Heure par heure'!E94-N('Heure par heure'!E93))</f>
+        <v/>
+      </c>
+      <c r="E94" s="3">
+        <f>SUM(B94:D94)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$94</f>
+              <f>'Heure par heure'!$C$2:$C$95</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$94</f>
+              <f>'Heure par heure'!$D$2:$D$95</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$94</f>
+              <f>'Heure par heure'!$E$2:$E$95</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$94</f>
+              <f>'Heure par heure'!$B$2:$B$95</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$94</f>
+              <f>'Heure par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$94</f>
+              <f>'Heure par heure'!$F$2:$F$95</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$94</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$95</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$94</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$95</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$94</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$94</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$95</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5490,6 +5490,29 @@
         <v/>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:00</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F95" s="3">
+        <f>SUM(C95:E95)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5502,7 +5525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7573,6 +7596,28 @@
       </c>
       <c r="E94" s="3">
         <f>SUM(B94:D94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <f>'Heure par heure'!A95</f>
+        <v/>
+      </c>
+      <c r="B95" s="3">
+        <f>IF('Heure par heure'!C95="","",'Heure par heure'!C95-N('Heure par heure'!C94))</f>
+        <v/>
+      </c>
+      <c r="C95" s="3">
+        <f>IF('Heure par heure'!D95="","",'Heure par heure'!D95-N('Heure par heure'!D94))</f>
+        <v/>
+      </c>
+      <c r="D95" s="3">
+        <f>IF('Heure par heure'!E95="","",'Heure par heure'!E95-N('Heure par heure'!E94))</f>
+        <v/>
+      </c>
+      <c r="E95" s="3">
+        <f>SUM(B95:D95)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$95</f>
+              <f>'Heure par heure'!$C$2:$C$96</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$95</f>
+              <f>'Heure par heure'!$D$2:$D$96</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$95</f>
+              <f>'Heure par heure'!$E$2:$E$96</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$95</f>
+              <f>'Heure par heure'!$B$2:$B$96</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$95</f>
+              <f>'Heure par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$95</f>
+              <f>'Heure par heure'!$F$2:$F$96</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$95</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$96</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$95</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$96</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$95</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$95</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$96</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>115</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5513,6 +5513,29 @@
         <v/>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:00</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F96" s="3">
+        <f>SUM(C96:E96)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5525,7 +5548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7618,6 +7641,28 @@
       </c>
       <c r="E95" s="3">
         <f>SUM(B95:D95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <f>'Heure par heure'!A96</f>
+        <v/>
+      </c>
+      <c r="B96" s="3">
+        <f>IF('Heure par heure'!C96="","",'Heure par heure'!C96-N('Heure par heure'!C95))</f>
+        <v/>
+      </c>
+      <c r="C96" s="3">
+        <f>IF('Heure par heure'!D96="","",'Heure par heure'!D96-N('Heure par heure'!D95))</f>
+        <v/>
+      </c>
+      <c r="D96" s="3">
+        <f>IF('Heure par heure'!E96="","",'Heure par heure'!E96-N('Heure par heure'!E95))</f>
+        <v/>
+      </c>
+      <c r="E96" s="3">
+        <f>SUM(B96:D96)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$96</f>
+              <f>'Heure par heure'!$C$2:$C$97</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$96</f>
+              <f>'Heure par heure'!$D$2:$D$97</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$96</f>
+              <f>'Heure par heure'!$E$2:$E$97</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$96</f>
+              <f>'Heure par heure'!$B$2:$B$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$96</f>
+              <f>'Heure par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$96</f>
+              <f>'Heure par heure'!$F$2:$F$97</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$96</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$97</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$96</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$97</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$96</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$96</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$97</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>115</row>
+      <row>116</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5536,6 +5536,29 @@
         <v/>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 06:00</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F97" s="3">
+        <f>SUM(C97:E97)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5548,7 +5571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7663,6 +7686,28 @@
       </c>
       <c r="E96" s="3">
         <f>SUM(B96:D96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <f>'Heure par heure'!A97</f>
+        <v/>
+      </c>
+      <c r="B97" s="3">
+        <f>IF('Heure par heure'!C97="","",'Heure par heure'!C97-N('Heure par heure'!C96))</f>
+        <v/>
+      </c>
+      <c r="C97" s="3">
+        <f>IF('Heure par heure'!D97="","",'Heure par heure'!D97-N('Heure par heure'!D96))</f>
+        <v/>
+      </c>
+      <c r="D97" s="3">
+        <f>IF('Heure par heure'!E97="","",'Heure par heure'!E97-N('Heure par heure'!E96))</f>
+        <v/>
+      </c>
+      <c r="E97" s="3">
+        <f>SUM(B97:D97)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$97</f>
+              <f>'Heure par heure'!$C$2:$C$98</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$97</f>
+              <f>'Heure par heure'!$D$2:$D$98</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$97</f>
+              <f>'Heure par heure'!$E$2:$E$98</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$97</f>
+              <f>'Heure par heure'!$B$2:$B$98</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$97</f>
+              <f>'Heure par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$97</f>
+              <f>'Heure par heure'!$F$2:$F$98</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$97</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$98</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$97</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$98</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$97</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$97</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$98</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>116</row>
+      <row>117</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5559,6 +5559,29 @@
         <v/>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 07:00</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F98" s="3">
+        <f>SUM(C98:E98)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5571,7 +5594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7708,6 +7731,28 @@
       </c>
       <c r="E97" s="3">
         <f>SUM(B97:D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <f>'Heure par heure'!A98</f>
+        <v/>
+      </c>
+      <c r="B98" s="3">
+        <f>IF('Heure par heure'!C98="","",'Heure par heure'!C98-N('Heure par heure'!C97))</f>
+        <v/>
+      </c>
+      <c r="C98" s="3">
+        <f>IF('Heure par heure'!D98="","",'Heure par heure'!D98-N('Heure par heure'!D97))</f>
+        <v/>
+      </c>
+      <c r="D98" s="3">
+        <f>IF('Heure par heure'!E98="","",'Heure par heure'!E98-N('Heure par heure'!E97))</f>
+        <v/>
+      </c>
+      <c r="E98" s="3">
+        <f>SUM(B98:D98)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$98</f>
+              <f>'Heure par heure'!$C$2:$C$99</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$98</f>
+              <f>'Heure par heure'!$D$2:$D$99</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$98</f>
+              <f>'Heure par heure'!$E$2:$E$99</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$98</f>
+              <f>'Heure par heure'!$B$2:$B$99</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$98</f>
+              <f>'Heure par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$98</f>
+              <f>'Heure par heure'!$F$2:$F$99</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$98</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$99</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$98</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$99</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$98</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$98</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$99</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>117</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5582,6 +5582,29 @@
         <v/>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 08:00</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F99" s="3">
+        <f>SUM(C99:E99)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5594,7 +5617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7753,6 +7776,28 @@
       </c>
       <c r="E98" s="3">
         <f>SUM(B98:D98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <f>'Heure par heure'!A99</f>
+        <v/>
+      </c>
+      <c r="B99" s="3">
+        <f>IF('Heure par heure'!C99="","",'Heure par heure'!C99-N('Heure par heure'!C98))</f>
+        <v/>
+      </c>
+      <c r="C99" s="3">
+        <f>IF('Heure par heure'!D99="","",'Heure par heure'!D99-N('Heure par heure'!D98))</f>
+        <v/>
+      </c>
+      <c r="D99" s="3">
+        <f>IF('Heure par heure'!E99="","",'Heure par heure'!E99-N('Heure par heure'!E98))</f>
+        <v/>
+      </c>
+      <c r="E99" s="3">
+        <f>SUM(B99:D99)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$B$2:$B$7</f>
+              <f>'Jour par jour'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -954,12 +954,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$E$2:$E$7</f>
+              <f>'Jour par jour'!$E$2:$E$8</f>
             </numRef>
           </val>
         </ser>
@@ -981,12 +981,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$L$2:$L$7</f>
+              <f>'Jour par jour'!$L$2:$L$8</f>
             </numRef>
           </val>
         </ser>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$F$2:$F$7</f>
+              <f>'Jour par jour'!$F$2:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1134,12 +1134,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$H$2:$H$7</f>
+              <f>'Jour par jour'!$H$2:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1236,12 +1236,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jour par jour'!$A$2:$A$7</f>
+              <f>'Jour par jour'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jour par jour'!$C$2:$C$7</f>
+              <f>'Jour par jour'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1729,12 +1729,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$B$2:$B$7</f>
+              <f>'Évolution par vidéo'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1761,12 +1761,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$C$2:$C$7</f>
+              <f>'Évolution par vidéo'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1793,12 +1793,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Évolution par vidéo'!$A$2:$A$7</f>
+              <f>'Évolution par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Évolution par vidéo'!$D$2:$D$7</f>
+              <f>'Évolution par vidéo'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -1891,12 +1891,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$B$2:$B$7</f>
+              <f>'Vues du jour par vidéo'!$B$2:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -1915,12 +1915,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$C$2:$C$7</f>
+              <f>'Vues du jour par vidéo'!$C$2:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -1939,12 +1939,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues du jour par vidéo'!$A$2:$A$7</f>
+              <f>'Vues du jour par vidéo'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues du jour par vidéo'!$D$2:$D$7</f>
+              <f>'Vues du jour par vidéo'!$D$2:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -2157,7 +2157,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2184,7 +2184,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7920000" cy="3240000"/>
@@ -2619,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2971,6 +2971,51 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(ROW()=2,"",B8-B7)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>337</v>
+      </c>
+      <c r="E8" s="3">
+        <f>IF(ROW()=2,D8,D8-D7)</f>
+        <v/>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3220,7 +3265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3328,6 +3373,22 @@
         <v>101</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>116</v>
       </c>
     </row>
@@ -3343,7 +3404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3515,6 +3576,29 @@
       </c>
       <c r="E7" s="3">
         <f>SUM(B7:D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>IF('Évolution par vidéo'!B8="","",'Évolution par vidéo'!B8-N('Évolution par vidéo'!B7))</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF('Évolution par vidéo'!C8="","",'Évolution par vidéo'!C8-N('Évolution par vidéo'!C7))</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF('Évolution par vidéo'!D8="","",'Évolution par vidéo'!D8-N('Évolution par vidéo'!D7))</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM(B8:D8)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$99</f>
+              <f>'Heure par heure'!$C$2:$C$100</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$99</f>
+              <f>'Heure par heure'!$D$2:$D$100</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$99</f>
+              <f>'Heure par heure'!$E$2:$E$100</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$99</f>
+              <f>'Heure par heure'!$B$2:$B$100</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$99</f>
+              <f>'Heure par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$99</f>
+              <f>'Heure par heure'!$F$2:$F$100</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$99</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$100</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$99</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$100</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$99</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$99</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$100</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>118</row>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3614,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5689,6 +5689,29 @@
         <v/>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 09:00</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F100" s="3">
+        <f>SUM(C100:E100)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5701,7 +5724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7882,6 +7905,28 @@
       </c>
       <c r="E99" s="3">
         <f>SUM(B99:D99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <f>'Heure par heure'!A100</f>
+        <v/>
+      </c>
+      <c r="B100" s="3">
+        <f>IF('Heure par heure'!C100="","",'Heure par heure'!C100-N('Heure par heure'!C99))</f>
+        <v/>
+      </c>
+      <c r="C100" s="3">
+        <f>IF('Heure par heure'!D100="","",'Heure par heure'!D100-N('Heure par heure'!D99))</f>
+        <v/>
+      </c>
+      <c r="D100" s="3">
+        <f>IF('Heure par heure'!E100="","",'Heure par heure'!E100-N('Heure par heure'!E99))</f>
+        <v/>
+      </c>
+      <c r="E100" s="3">
+        <f>SUM(B100:D100)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$100</f>
+              <f>'Heure par heure'!$C$2:$C$101</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$100</f>
+              <f>'Heure par heure'!$D$2:$D$101</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$100</f>
+              <f>'Heure par heure'!$E$2:$E$101</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$100</f>
+              <f>'Heure par heure'!$B$2:$B$101</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$100</f>
+              <f>'Heure par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$100</f>
+              <f>'Heure par heure'!$F$2:$F$101</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$100</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$101</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$100</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$101</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$100</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$100</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$101</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>119</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>119</row>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3614,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5712,6 +5712,29 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 10:00</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F101" s="3">
+        <f>SUM(C101:E101)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5724,7 +5747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7927,6 +7950,28 @@
       </c>
       <c r="E100" s="3">
         <f>SUM(B100:D100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <f>'Heure par heure'!A101</f>
+        <v/>
+      </c>
+      <c r="B101" s="3">
+        <f>IF('Heure par heure'!C101="","",'Heure par heure'!C101-N('Heure par heure'!C100))</f>
+        <v/>
+      </c>
+      <c r="C101" s="3">
+        <f>IF('Heure par heure'!D101="","",'Heure par heure'!D101-N('Heure par heure'!D100))</f>
+        <v/>
+      </c>
+      <c r="D101" s="3">
+        <f>IF('Heure par heure'!E101="","",'Heure par heure'!E101-N('Heure par heure'!E100))</f>
+        <v/>
+      </c>
+      <c r="E101" s="3">
+        <f>SUM(B101:D101)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$101</f>
+              <f>'Heure par heure'!$C$2:$C$102</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$101</f>
+              <f>'Heure par heure'!$D$2:$D$102</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$101</f>
+              <f>'Heure par heure'!$E$2:$E$102</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$101</f>
+              <f>'Heure par heure'!$B$2:$B$102</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$101</f>
+              <f>'Heure par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$101</f>
+              <f>'Heure par heure'!$F$2:$F$102</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$101</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$102</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$101</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$102</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$101</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$101</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$102</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>120</row>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3614,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5735,6 +5735,29 @@
         <v/>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 11:00</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F102" s="3">
+        <f>SUM(C102:E102)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5747,7 +5770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7972,6 +7995,28 @@
       </c>
       <c r="E101" s="3">
         <f>SUM(B101:D101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <f>'Heure par heure'!A102</f>
+        <v/>
+      </c>
+      <c r="B102" s="3">
+        <f>IF('Heure par heure'!C102="","",'Heure par heure'!C102-N('Heure par heure'!C101))</f>
+        <v/>
+      </c>
+      <c r="C102" s="3">
+        <f>IF('Heure par heure'!D102="","",'Heure par heure'!D102-N('Heure par heure'!D101))</f>
+        <v/>
+      </c>
+      <c r="D102" s="3">
+        <f>IF('Heure par heure'!E102="","",'Heure par heure'!E102-N('Heure par heure'!E101))</f>
+        <v/>
+      </c>
+      <c r="E102" s="3">
+        <f>SUM(B102:D102)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$102</f>
+              <f>'Heure par heure'!$C$2:$C$103</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$102</f>
+              <f>'Heure par heure'!$D$2:$D$103</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$102</f>
+              <f>'Heure par heure'!$E$2:$E$103</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$102</f>
+              <f>'Heure par heure'!$B$2:$B$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$102</f>
+              <f>'Heure par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$102</f>
+              <f>'Heure par heure'!$F$2:$F$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$102</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$103</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$102</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$103</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$102</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$102</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$103</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>121</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3614,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5758,6 +5758,29 @@
         <v/>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 12:00</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F103" s="3">
+        <f>SUM(C103:E103)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5770,7 +5793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8017,6 +8040,28 @@
       </c>
       <c r="E102" s="3">
         <f>SUM(B102:D102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <f>'Heure par heure'!A103</f>
+        <v/>
+      </c>
+      <c r="B103" s="3">
+        <f>IF('Heure par heure'!C103="","",'Heure par heure'!C103-N('Heure par heure'!C102))</f>
+        <v/>
+      </c>
+      <c r="C103" s="3">
+        <f>IF('Heure par heure'!D103="","",'Heure par heure'!D103-N('Heure par heure'!D102))</f>
+        <v/>
+      </c>
+      <c r="D103" s="3">
+        <f>IF('Heure par heure'!E103="","",'Heure par heure'!E103-N('Heure par heure'!E102))</f>
+        <v/>
+      </c>
+      <c r="E103" s="3">
+        <f>SUM(B103:D103)</f>
         <v/>
       </c>
     </row>

--- a/suivi/Decode_suivi_science.xlsx
+++ b/suivi/Decode_suivi_science.xlsx
@@ -328,12 +328,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$103</f>
+              <f>'Heure par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$C$2:$C$103</f>
+              <f>'Heure par heure'!$C$2:$C$104</f>
             </numRef>
           </val>
         </ser>
@@ -360,12 +360,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$103</f>
+              <f>'Heure par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$D$2:$D$103</f>
+              <f>'Heure par heure'!$D$2:$D$104</f>
             </numRef>
           </val>
         </ser>
@@ -392,12 +392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$103</f>
+              <f>'Heure par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$E$2:$E$103</f>
+              <f>'Heure par heure'!$E$2:$E$104</f>
             </numRef>
           </val>
         </ser>
@@ -504,12 +504,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$103</f>
+              <f>'Heure par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$B$2:$B$103</f>
+              <f>'Heure par heure'!$B$2:$B$104</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -617,12 +617,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Heure par heure'!$A$2:$A$103</f>
+              <f>'Heure par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Heure par heure'!$F$2:$F$103</f>
+              <f>'Heure par heure'!$F$2:$F$104</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -716,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$B$2:$B$103</f>
+              <f>'Vues gagnées par heure'!$B$2:$B$104</f>
             </numRef>
           </val>
         </ser>
@@ -740,12 +740,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$C$2:$C$103</f>
+              <f>'Vues gagnées par heure'!$C$2:$C$104</f>
             </numRef>
           </val>
         </ser>
@@ -764,12 +764,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Vues gagnées par heure'!$A$2:$A$103</f>
+              <f>'Vues gagnées par heure'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Vues gagnées par heure'!$D$2:$D$103</f>
+              <f>'Vues gagnées par heure'!$D$2:$D$104</f>
             </numRef>
           </val>
         </ser>
@@ -2211,7 +2211,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2233,7 +2233,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>122</row>
+      <row>123</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2255,7 +2255,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>122</row>
+      <row>123</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2700000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3240000"/>
@@ -3614,7 +3614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5781,6 +5781,29 @@
         <v/>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31 13:00</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F104" s="3">
+        <f>SUM(C104:E104)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5793,7 +5816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8062,6 +8085,28 @@
       </c>
       <c r="E103" s="3">
         <f>SUM(B103:D103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <f>'Heure par heure'!A104</f>
+        <v/>
+      </c>
+      <c r="B104" s="3">
+        <f>IF('Heure par heure'!C104="","",'Heure par heure'!C104-N('Heure par heure'!C103))</f>
+        <v/>
+      </c>
+      <c r="C104" s="3">
+        <f>IF('Heure par heure'!D104="","",'Heure par heure'!D104-N('Heure par heure'!D103))</f>
+        <v/>
+      </c>
+      <c r="D104" s="3">
+        <f>IF('Heure par heure'!E104="","",'Heure par heure'!E104-N('Heure par heure'!E103))</f>
+        <v/>
+      </c>
+      <c r="E104" s="3">
+        <f>SUM(B104:D104)</f>
         <v/>
       </c>
     </row>
